--- a/stella/test_fixtures/strong_promo/iri_data.xlsx
+++ b/stella/test_fixtures/strong_promo/iri_data.xlsx
@@ -2083,19 +2083,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13134.17</v>
+        <v>13863.85</v>
       </c>
       <c r="E46" t="n">
-        <v>350.2</v>
+        <v>369.7</v>
       </c>
       <c r="F46" t="n">
         <v>6.25</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2335</v>
+        <v>0.2402</v>
       </c>
       <c r="H46" t="n">
-        <v>0.233</v>
+        <v>0.2396</v>
       </c>
       <c r="I46" t="n">
         <v>90</v>
@@ -2119,19 +2119,19 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13501.13</v>
+        <v>14251.19</v>
       </c>
       <c r="E47" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="F47" t="n">
         <v>6.25</v>
       </c>
       <c r="G47" t="n">
-        <v>0.24</v>
+        <v>0.2469</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2395</v>
+        <v>0.2463</v>
       </c>
       <c r="I47" t="n">
         <v>89</v>
@@ -2164,10 +2164,10 @@
         <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>0.28</v>
+        <v>0.2728</v>
       </c>
       <c r="H48" t="n">
-        <v>0.291</v>
+        <v>0.2836</v>
       </c>
       <c r="I48" t="n">
         <v>89</v>
@@ -2200,10 +2200,10 @@
         <v>6.5</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2465</v>
+        <v>0.2402</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2365</v>
+        <v>0.2304</v>
       </c>
       <c r="I49" t="n">
         <v>91</v>
@@ -2227,19 +2227,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14537.49</v>
+        <v>15575.88</v>
       </c>
       <c r="E50" t="n">
-        <v>387.7</v>
+        <v>415.4</v>
       </c>
       <c r="F50" t="n">
         <v>6.25</v>
       </c>
       <c r="G50" t="n">
-        <v>0.248</v>
+        <v>0.2646</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2476</v>
+        <v>0.2641</v>
       </c>
       <c r="I50" t="n">
         <v>92</v>
@@ -2263,19 +2263,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14215.08</v>
+        <v>15230.44</v>
       </c>
       <c r="E51" t="n">
-        <v>379.1</v>
+        <v>406.1</v>
       </c>
       <c r="F51" t="n">
         <v>6.25</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2425</v>
+        <v>0.2587</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2421</v>
+        <v>0.2582</v>
       </c>
       <c r="I51" t="n">
         <v>91</v>
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15704.94</v>
+        <v>14762.64</v>
       </c>
       <c r="E52" t="n">
-        <v>436.2</v>
+        <v>410.1</v>
       </c>
       <c r="F52" t="n">
         <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2679</v>
+        <v>0.2507</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2786</v>
+        <v>0.2607</v>
       </c>
       <c r="I52" t="n">
         <v>89</v>
@@ -2335,19 +2335,19 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14154.39</v>
+        <v>13305.13</v>
       </c>
       <c r="E53" t="n">
-        <v>362.9</v>
+        <v>341.2</v>
       </c>
       <c r="F53" t="n">
         <v>6.5</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2415</v>
+        <v>0.226</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2318</v>
+        <v>0.2169</v>
       </c>
       <c r="I53" t="n">
         <v>92</v>
@@ -2371,19 +2371,19 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15027.81</v>
+        <v>16101.23</v>
       </c>
       <c r="E54" t="n">
-        <v>400.7</v>
+        <v>429.4</v>
       </c>
       <c r="F54" t="n">
         <v>6.25</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2525</v>
+        <v>0.2689</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2518</v>
+        <v>0.2682</v>
       </c>
       <c r="I54" t="n">
         <v>88</v>
@@ -2407,19 +2407,19 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14955.06</v>
+        <v>16023.28</v>
       </c>
       <c r="E55" t="n">
-        <v>398.8</v>
+        <v>427.3</v>
       </c>
       <c r="F55" t="n">
         <v>6.25</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2513</v>
+        <v>0.2676</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2506</v>
+        <v>0.2669</v>
       </c>
       <c r="I55" t="n">
         <v>92</v>
@@ -2443,19 +2443,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>16134.37</v>
+        <v>15166.31</v>
       </c>
       <c r="E56" t="n">
-        <v>448.2</v>
+        <v>421.3</v>
       </c>
       <c r="F56" t="n">
         <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2711</v>
+        <v>0.2532</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2816</v>
+        <v>0.2631</v>
       </c>
       <c r="I56" t="n">
         <v>90</v>
@@ -2479,19 +2479,19 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13401.29</v>
+        <v>12597.21</v>
       </c>
       <c r="E57" t="n">
-        <v>343.6</v>
+        <v>323</v>
       </c>
       <c r="F57" t="n">
         <v>6.5</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2252</v>
+        <v>0.2103</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2159</v>
+        <v>0.2018</v>
       </c>
       <c r="I57" t="n">
         <v>89</v>
@@ -2515,19 +2515,19 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14471.8</v>
+        <v>15505.51</v>
       </c>
       <c r="E58" t="n">
-        <v>385.9</v>
+        <v>413.5</v>
       </c>
       <c r="F58" t="n">
         <v>6.25</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2449</v>
+        <v>0.2611</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2444</v>
+        <v>0.2606</v>
       </c>
       <c r="I58" t="n">
         <v>91</v>
@@ -2551,19 +2551,19 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14793.16</v>
+        <v>15849.82</v>
       </c>
       <c r="E59" t="n">
-        <v>394.5</v>
+        <v>422.7</v>
       </c>
       <c r="F59" t="n">
         <v>6.25</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2504</v>
+        <v>0.2669</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2499</v>
+        <v>0.2664</v>
       </c>
       <c r="I59" t="n">
         <v>91</v>
@@ -2587,19 +2587,19 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>15781.1</v>
+        <v>14834.23</v>
       </c>
       <c r="E60" t="n">
-        <v>438.4</v>
+        <v>412.1</v>
       </c>
       <c r="F60" t="n">
         <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2671</v>
+        <v>0.2498</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2777</v>
+        <v>0.2597</v>
       </c>
       <c r="I60" t="n">
         <v>90</v>
@@ -2623,19 +2623,19 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14039.42</v>
+        <v>13197.06</v>
       </c>
       <c r="E61" t="n">
-        <v>360</v>
+        <v>338.4</v>
       </c>
       <c r="F61" t="n">
         <v>6.5</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2376</v>
+        <v>0.2222</v>
       </c>
       <c r="H61" t="n">
-        <v>0.228</v>
+        <v>0.2133</v>
       </c>
       <c r="I61" t="n">
         <v>91</v>
@@ -2659,19 +2659,19 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14798.9</v>
+        <v>15855.96</v>
       </c>
       <c r="E62" t="n">
-        <v>394.6</v>
+        <v>422.8</v>
       </c>
       <c r="F62" t="n">
         <v>6.25</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2513</v>
+        <v>0.2676</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2507</v>
+        <v>0.267</v>
       </c>
       <c r="I62" t="n">
         <v>88</v>
@@ -2695,19 +2695,19 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14876.22</v>
+        <v>15938.81</v>
       </c>
       <c r="E63" t="n">
-        <v>396.7</v>
+        <v>425</v>
       </c>
       <c r="F63" t="n">
         <v>6.25</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2526</v>
+        <v>0.269</v>
       </c>
       <c r="H63" t="n">
-        <v>0.252</v>
+        <v>0.2684</v>
       </c>
       <c r="I63" t="n">
         <v>90</v>
@@ -2731,19 +2731,19 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15661.44</v>
+        <v>14721.75</v>
       </c>
       <c r="E64" t="n">
-        <v>435</v>
+        <v>408.9</v>
       </c>
       <c r="F64" t="n">
         <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2659</v>
+        <v>0.2484</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2764</v>
+        <v>0.2582</v>
       </c>
       <c r="I64" t="n">
         <v>89</v>
@@ -2767,19 +2767,19 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13558.06</v>
+        <v>12744.58</v>
       </c>
       <c r="E65" t="n">
-        <v>347.6</v>
+        <v>326.8</v>
       </c>
       <c r="F65" t="n">
         <v>6.5</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2302</v>
+        <v>0.2151</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2209</v>
+        <v>0.2064</v>
       </c>
       <c r="I65" t="n">
         <v>88</v>

--- a/stella/test_fixtures/strong_promo/iri_data.xlsx
+++ b/stella/test_fixtures/strong_promo/iri_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,26 +495,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15328.75</v>
+        <v>17676.6</v>
       </c>
       <c r="E2" t="n">
-        <v>408.8</v>
+        <v>2810.3</v>
       </c>
       <c r="F2" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2522</v>
+        <v>0.0761</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2515</v>
+        <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -531,26 +531,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14926.65</v>
+        <v>17212.92</v>
       </c>
       <c r="E3" t="n">
-        <v>398</v>
+        <v>2736.6</v>
       </c>
       <c r="F3" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2456</v>
+        <v>0.0741</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2449</v>
+        <v>0.053</v>
       </c>
       <c r="I3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -562,31 +562,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16664.74</v>
+        <v>17793.73</v>
       </c>
       <c r="E4" t="n">
-        <v>462.9</v>
+        <v>2828.9</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2742</v>
+        <v>0.0766</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2848</v>
+        <v>0.0548</v>
       </c>
       <c r="I4" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -598,31 +598,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13865.53</v>
+        <v>16316.37</v>
       </c>
       <c r="E5" t="n">
-        <v>355.5</v>
+        <v>2514.1</v>
       </c>
       <c r="F5" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2281</v>
+        <v>0.0702</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2188</v>
+        <v>0.0487</v>
       </c>
       <c r="I5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -630,32 +630,32 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14553.74</v>
+        <v>15541.26</v>
       </c>
       <c r="E6" t="n">
-        <v>388.1</v>
+        <v>2394.6</v>
       </c>
       <c r="F6" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G6" t="n">
-        <v>0.244</v>
+        <v>0.0669</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2435</v>
+        <v>0.0464</v>
       </c>
       <c r="I6" t="n">
         <v>91</v>
@@ -666,35 +666,35 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14940.46</v>
+        <v>16673.93</v>
       </c>
       <c r="E7" t="n">
-        <v>398.4</v>
+        <v>2569.2</v>
       </c>
       <c r="F7" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2505</v>
+        <v>0.0718</v>
       </c>
       <c r="H7" t="n">
-        <v>0.25</v>
+        <v>0.0498</v>
       </c>
       <c r="I7" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -702,35 +702,35 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16032.55</v>
+        <v>16861.55</v>
       </c>
       <c r="E8" t="n">
-        <v>445.3</v>
+        <v>3930.4</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2688</v>
+        <v>0.0726</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2794</v>
+        <v>0.0762</v>
       </c>
       <c r="I8" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -738,35 +738,35 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14116.03</v>
+        <v>16894.48</v>
       </c>
       <c r="E9" t="n">
-        <v>361.9</v>
+        <v>3938.1</v>
       </c>
       <c r="F9" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2367</v>
+        <v>0.0727</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2271</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -774,35 +774,35 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15065.5</v>
+        <v>16025.12</v>
       </c>
       <c r="E10" t="n">
-        <v>401.7</v>
+        <v>3735.5</v>
       </c>
       <c r="F10" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2513</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2506</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -810,35 +810,35 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14476.58</v>
+        <v>14563.71</v>
       </c>
       <c r="E11" t="n">
-        <v>386</v>
+        <v>3560.8</v>
       </c>
       <c r="F11" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2414</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2408</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -846,35 +846,35 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16624.61</v>
+        <v>14470.62</v>
       </c>
       <c r="E12" t="n">
-        <v>461.8</v>
+        <v>3538</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2773</v>
+        <v>0.0623</v>
       </c>
       <c r="H12" t="n">
-        <v>0.288</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -882,35 +882,35 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13793.78</v>
+        <v>15120.95</v>
       </c>
       <c r="E13" t="n">
-        <v>353.7</v>
+        <v>3697.1</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G13" t="n">
-        <v>0.23</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2206</v>
+        <v>0.0717</v>
       </c>
       <c r="I13" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -918,32 +918,32 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15334.06</v>
+        <v>12417.29</v>
       </c>
       <c r="E14" t="n">
-        <v>408.9</v>
+        <v>4450.6</v>
       </c>
       <c r="F14" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2587</v>
+        <v>0.0534</v>
       </c>
       <c r="H14" t="n">
-        <v>0.258</v>
+        <v>0.0863</v>
       </c>
       <c r="I14" t="n">
         <v>88</v>
@@ -954,35 +954,35 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14633.57</v>
+        <v>12592.98</v>
       </c>
       <c r="E15" t="n">
-        <v>390.2</v>
+        <v>4513.6</v>
       </c>
       <c r="F15" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2469</v>
+        <v>0.0542</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2462</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -990,32 +990,32 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16156.87</v>
+        <v>12220.43</v>
       </c>
       <c r="E16" t="n">
-        <v>448.8</v>
+        <v>4380.1</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2726</v>
+        <v>0.0526</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2831</v>
+        <v>0.0849</v>
       </c>
       <c r="I16" t="n">
         <v>91</v>
@@ -1026,35 +1026,35 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45682</v>
+        <v>45668</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13151.83</v>
+        <v>17636.2</v>
       </c>
       <c r="E17" t="n">
-        <v>337.2</v>
+        <v>2803.8</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2219</v>
+        <v>0.0765</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2127</v>
+        <v>0.0547</v>
       </c>
       <c r="I17" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1071,34 +1071,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28398.7</v>
+        <v>17944.44</v>
       </c>
       <c r="E18" t="n">
-        <v>946.6</v>
+        <v>2852.9</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3396</v>
+        <v>0.0779</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3623</v>
+        <v>0.0557</v>
       </c>
       <c r="I18" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1107,62 +1107,62 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>28501.54</v>
+        <v>17056.48</v>
       </c>
       <c r="E19" t="n">
-        <v>950.1</v>
+        <v>2711.7</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3408</v>
+        <v>0.074</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3637</v>
+        <v>0.0529</v>
       </c>
       <c r="I19" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14221.28</v>
+        <v>15896.29</v>
       </c>
       <c r="E20" t="n">
-        <v>395</v>
+        <v>2449.4</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G20" t="n">
-        <v>0.17</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1512</v>
+        <v>0.0478</v>
       </c>
       <c r="I20" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1170,35 +1170,35 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12512.25</v>
+        <v>16023.63</v>
       </c>
       <c r="E21" t="n">
-        <v>320.8</v>
+        <v>2469</v>
       </c>
       <c r="F21" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1496</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1228</v>
+        <v>0.0482</v>
       </c>
       <c r="I21" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1206,107 +1206,107 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>28655.2</v>
+        <v>15663.71</v>
       </c>
       <c r="E22" t="n">
-        <v>955.2</v>
+        <v>2413.5</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6.49</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3358</v>
+        <v>0.068</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3581</v>
+        <v>0.0471</v>
       </c>
       <c r="I22" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29566.49</v>
+        <v>16027.51</v>
       </c>
       <c r="E23" t="n">
-        <v>985.5</v>
+        <v>3736</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4.29</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3464</v>
+        <v>0.0696</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3695</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14484.4</v>
+        <v>16484.4</v>
       </c>
       <c r="E24" t="n">
-        <v>402.3</v>
+        <v>3842.5</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1697</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1509</v>
+        <v>0.075</v>
       </c>
       <c r="I24" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1314,35 +1314,35 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12638.4</v>
+        <v>16155.66</v>
       </c>
       <c r="E25" t="n">
-        <v>324.1</v>
+        <v>3765.9</v>
       </c>
       <c r="F25" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1481</v>
+        <v>0.0701</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1215</v>
+        <v>0.0735</v>
       </c>
       <c r="I25" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1350,107 +1350,107 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29220.47</v>
+        <v>14820.39</v>
       </c>
       <c r="E26" t="n">
-        <v>974</v>
+        <v>3623.6</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3502</v>
+        <v>0.0643</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3733</v>
+        <v>0.0707</v>
       </c>
       <c r="I26" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>27969.99</v>
+        <v>14548.23</v>
       </c>
       <c r="E27" t="n">
-        <v>932.3</v>
+        <v>3557</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3353</v>
+        <v>0.0631</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3574</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>91</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13913.75</v>
+        <v>15010.9</v>
       </c>
       <c r="E28" t="n">
-        <v>386.5</v>
+        <v>3670.1</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1668</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1481</v>
+        <v>0.0717</v>
       </c>
       <c r="I28" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1458,35 +1458,35 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12325.32</v>
+        <v>12472.68</v>
       </c>
       <c r="E29" t="n">
-        <v>316</v>
+        <v>4470.5</v>
       </c>
       <c r="F29" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1477</v>
+        <v>0.0541</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1211</v>
+        <v>0.0873</v>
       </c>
       <c r="I29" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1494,107 +1494,107 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45710</v>
+        <v>45668</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28705.34</v>
+        <v>12091.73</v>
       </c>
       <c r="E30" t="n">
-        <v>956.8</v>
+        <v>4334</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>2.79</v>
       </c>
       <c r="G30" t="n">
-        <v>0.342</v>
+        <v>0.0525</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3644</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45710</v>
+        <v>45668</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28958.38</v>
+        <v>12602.31</v>
       </c>
       <c r="E31" t="n">
-        <v>965.3</v>
+        <v>4517</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>2.79</v>
       </c>
       <c r="G31" t="n">
-        <v>0.345</v>
+        <v>0.0547</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3676</v>
+        <v>0.0882</v>
       </c>
       <c r="I31" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45710</v>
+        <v>45675</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13845.2</v>
+        <v>17530.54</v>
       </c>
       <c r="E32" t="n">
-        <v>384.6</v>
+        <v>2787</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1649</v>
+        <v>0.0764</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1465</v>
+        <v>0.0548</v>
       </c>
       <c r="I32" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1602,35 +1602,35 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45710</v>
+        <v>45675</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12435.32</v>
+        <v>17257.5</v>
       </c>
       <c r="E33" t="n">
-        <v>318.9</v>
+        <v>2743.6</v>
       </c>
       <c r="F33" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1481</v>
+        <v>0.0752</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1214</v>
+        <v>0.054</v>
       </c>
       <c r="I33" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1647,26 +1647,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12887.41</v>
+        <v>17387.77</v>
       </c>
       <c r="E34" t="n">
-        <v>343.7</v>
+        <v>2764.4</v>
       </c>
       <c r="F34" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2326</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2319</v>
+        <v>0.0544</v>
       </c>
       <c r="I34" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1674,32 +1674,32 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12804.65</v>
+        <v>16403.28</v>
       </c>
       <c r="E35" t="n">
-        <v>341.5</v>
+        <v>2527.5</v>
       </c>
       <c r="F35" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2311</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2304</v>
+        <v>0.0497</v>
       </c>
       <c r="I35" t="n">
         <v>90</v>
@@ -1710,35 +1710,35 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16276.73</v>
+        <v>16235.87</v>
       </c>
       <c r="E36" t="n">
-        <v>452.1</v>
+        <v>2501.7</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2938</v>
+        <v>0.0707</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3051</v>
+        <v>0.0492</v>
       </c>
       <c r="I36" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1746,35 +1746,35 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13435.91</v>
+        <v>16131.6</v>
       </c>
       <c r="E37" t="n">
-        <v>344.5</v>
+        <v>2485.6</v>
       </c>
       <c r="F37" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2425</v>
+        <v>0.0703</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2325</v>
+        <v>0.0489</v>
       </c>
       <c r="I37" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1782,35 +1782,35 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13110.47</v>
+        <v>16594.73</v>
       </c>
       <c r="E38" t="n">
-        <v>349.6</v>
+        <v>3868.2</v>
       </c>
       <c r="F38" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G38" t="n">
-        <v>0.24</v>
+        <v>0.0723</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2394</v>
+        <v>0.0761</v>
       </c>
       <c r="I38" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1818,35 +1818,35 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12478.62</v>
+        <v>16257.46</v>
       </c>
       <c r="E39" t="n">
-        <v>332.8</v>
+        <v>3789.6</v>
       </c>
       <c r="F39" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2284</v>
+        <v>0.0708</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2279</v>
+        <v>0.0745</v>
       </c>
       <c r="I39" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -1854,35 +1854,35 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15627.56</v>
+        <v>15896.56</v>
       </c>
       <c r="E40" t="n">
-        <v>434.1</v>
+        <v>3705.5</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2861</v>
+        <v>0.0693</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2973</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -1890,35 +1890,35 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13411.27</v>
+        <v>14547.73</v>
       </c>
       <c r="E41" t="n">
-        <v>343.9</v>
+        <v>3556.9</v>
       </c>
       <c r="F41" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2455</v>
+        <v>0.0634</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2355</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -1926,32 +1926,32 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13677.46</v>
+        <v>14287.89</v>
       </c>
       <c r="E42" t="n">
-        <v>364.7</v>
+        <v>3493.4</v>
       </c>
       <c r="F42" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2401</v>
+        <v>0.0622</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2393</v>
+        <v>0.0687</v>
       </c>
       <c r="I42" t="n">
         <v>88</v>
@@ -1962,35 +1962,35 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13398.9</v>
+        <v>14514.75</v>
       </c>
       <c r="E43" t="n">
-        <v>357.3</v>
+        <v>3548.8</v>
       </c>
       <c r="F43" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2352</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2344</v>
+        <v>0.0698</v>
       </c>
       <c r="I43" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -1998,35 +1998,35 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16606.97</v>
+        <v>12623.07</v>
       </c>
       <c r="E44" t="n">
-        <v>461.3</v>
+        <v>4524.4</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2915</v>
+        <v>0.055</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3027</v>
+        <v>0.089</v>
       </c>
       <c r="I44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2034,35 +2034,35 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13286.33</v>
+        <v>12014.71</v>
       </c>
       <c r="E45" t="n">
-        <v>340.7</v>
+        <v>4306.3</v>
       </c>
       <c r="F45" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2332</v>
+        <v>0.0523</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2235</v>
+        <v>0.0847</v>
       </c>
       <c r="I45" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2070,32 +2070,32 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45738</v>
+        <v>45675</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13863.85</v>
+        <v>11842.22</v>
       </c>
       <c r="E46" t="n">
-        <v>369.7</v>
+        <v>4244.5</v>
       </c>
       <c r="F46" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2402</v>
+        <v>0.0516</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2396</v>
+        <v>0.0835</v>
       </c>
       <c r="I46" t="n">
         <v>90</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2115,26 +2115,26 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14251.19</v>
+        <v>16816.37</v>
       </c>
       <c r="E47" t="n">
-        <v>380</v>
+        <v>2673.5</v>
       </c>
       <c r="F47" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2469</v>
+        <v>0.073</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2463</v>
+        <v>0.0521</v>
       </c>
       <c r="I47" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2142,35 +2142,35 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>15749.4</v>
+        <v>17569.17</v>
       </c>
       <c r="E48" t="n">
-        <v>437.5</v>
+        <v>2793.2</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2728</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2836</v>
+        <v>0.0545</v>
       </c>
       <c r="I48" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2178,35 +2178,35 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13864.38</v>
+        <v>17222.99</v>
       </c>
       <c r="E49" t="n">
-        <v>355.5</v>
+        <v>2738.2</v>
       </c>
       <c r="F49" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2402</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2304</v>
+        <v>0.0534</v>
       </c>
       <c r="I49" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2214,35 +2214,35 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15575.88</v>
+        <v>15909.86</v>
       </c>
       <c r="E50" t="n">
-        <v>415.4</v>
+        <v>2451.4</v>
       </c>
       <c r="F50" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2646</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2641</v>
+        <v>0.0478</v>
       </c>
       <c r="I50" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2250,35 +2250,35 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15230.44</v>
+        <v>15807.69</v>
       </c>
       <c r="E51" t="n">
-        <v>406.1</v>
+        <v>2435.7</v>
       </c>
       <c r="F51" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2587</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2582</v>
+        <v>0.0475</v>
       </c>
       <c r="I51" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2286,35 +2286,35 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14762.64</v>
+        <v>16230.17</v>
       </c>
       <c r="E52" t="n">
-        <v>410.1</v>
+        <v>2500.8</v>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2507</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2607</v>
+        <v>0.0488</v>
       </c>
       <c r="I52" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2322,35 +2322,35 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13305.13</v>
+        <v>16333.91</v>
       </c>
       <c r="E53" t="n">
-        <v>341.2</v>
+        <v>3807.4</v>
       </c>
       <c r="F53" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G53" t="n">
-        <v>0.226</v>
+        <v>0.0709</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2169</v>
+        <v>0.0743</v>
       </c>
       <c r="I53" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2358,35 +2358,35 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16101.23</v>
+        <v>15971.65</v>
       </c>
       <c r="E54" t="n">
-        <v>429.4</v>
+        <v>3723</v>
       </c>
       <c r="F54" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2689</v>
+        <v>0.0693</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2682</v>
+        <v>0.0726</v>
       </c>
       <c r="I54" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2394,35 +2394,35 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16023.28</v>
+        <v>16011.76</v>
       </c>
       <c r="E55" t="n">
-        <v>427.3</v>
+        <v>3732.3</v>
       </c>
       <c r="F55" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2676</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2669</v>
+        <v>0.0728</v>
       </c>
       <c r="I55" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2430,35 +2430,35 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15166.31</v>
+        <v>15162.05</v>
       </c>
       <c r="E56" t="n">
-        <v>421.3</v>
+        <v>3707.1</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2532</v>
+        <v>0.0658</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2631</v>
+        <v>0.0723</v>
       </c>
       <c r="I56" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -2466,35 +2466,35 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12597.21</v>
+        <v>15099.68</v>
       </c>
       <c r="E57" t="n">
-        <v>323</v>
+        <v>3691.9</v>
       </c>
       <c r="F57" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2103</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2018</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2502,32 +2502,32 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15505.51</v>
+        <v>14855.36</v>
       </c>
       <c r="E58" t="n">
-        <v>413.5</v>
+        <v>3632.1</v>
       </c>
       <c r="F58" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2611</v>
+        <v>0.0645</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2606</v>
+        <v>0.0708</v>
       </c>
       <c r="I58" t="n">
         <v>91</v>
@@ -2538,32 +2538,32 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>15849.82</v>
+        <v>12046.07</v>
       </c>
       <c r="E59" t="n">
-        <v>422.7</v>
+        <v>4317.6</v>
       </c>
       <c r="F59" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2669</v>
+        <v>0.0523</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2664</v>
+        <v>0.0842</v>
       </c>
       <c r="I59" t="n">
         <v>91</v>
@@ -2574,32 +2574,32 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14834.23</v>
+        <v>12736.77</v>
       </c>
       <c r="E60" t="n">
-        <v>412.1</v>
+        <v>4565.2</v>
       </c>
       <c r="F60" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2498</v>
+        <v>0.0553</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2597</v>
+        <v>0.089</v>
       </c>
       <c r="I60" t="n">
         <v>90</v>
@@ -2610,32 +2610,32 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13197.06</v>
+        <v>12549.76</v>
       </c>
       <c r="E61" t="n">
-        <v>338.4</v>
+        <v>4498.1</v>
       </c>
       <c r="F61" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2222</v>
+        <v>0.0545</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2133</v>
+        <v>0.0877</v>
       </c>
       <c r="I61" t="n">
         <v>91</v>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2655,34 +2655,34 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>15855.96</v>
+        <v>33487.79</v>
       </c>
       <c r="E62" t="n">
-        <v>422.8</v>
+        <v>6644.4</v>
       </c>
       <c r="F62" t="n">
-        <v>6.25</v>
+        <v>5.04</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2676</v>
+        <v>0.126</v>
       </c>
       <c r="H62" t="n">
-        <v>0.267</v>
+        <v>0.1103</v>
       </c>
       <c r="I62" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2691,100 +2691,6436 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>15938.81</v>
+        <v>33662.76</v>
       </c>
       <c r="E63" t="n">
-        <v>425</v>
+        <v>6679.1</v>
       </c>
       <c r="F63" t="n">
-        <v>6.25</v>
+        <v>5.04</v>
       </c>
       <c r="G63" t="n">
-        <v>0.269</v>
+        <v>0.1266</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2684</v>
+        <v>0.1108</v>
       </c>
       <c r="I63" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14721.75</v>
+        <v>32158.16</v>
       </c>
       <c r="E64" t="n">
-        <v>408.9</v>
+        <v>6380.6</v>
       </c>
       <c r="F64" t="n">
-        <v>6</v>
+        <v>5.04</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2484</v>
+        <v>0.121</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2582</v>
+        <v>0.1059</v>
       </c>
       <c r="I64" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>14040.01</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2163.3</v>
+      </c>
+      <c r="F65" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="I65" t="n">
+        <v>91</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>13616.87</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2098.1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.0512</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="I66" t="n">
+        <v>88</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>14128.42</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2177</v>
+      </c>
+      <c r="F67" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="I67" t="n">
+        <v>90</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>15477.11</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3607.7</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="I68" t="n">
+        <v>90</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>15244.46</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3553.5</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="I69" t="n">
+        <v>92</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>15192.84</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3541.5</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="I70" t="n">
+        <v>90</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>14135.3</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3456.1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="I71" t="n">
+        <v>90</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>13666.97</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3341.6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.0554</v>
+      </c>
+      <c r="I72" t="n">
+        <v>89</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>14514.27</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3548.7</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="I73" t="n">
+        <v>89</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>12232.05</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4384.2</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="I74" t="n">
+        <v>90</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>12004.36</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4302.6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="I75" t="n">
+        <v>90</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>12241.63</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4387.7</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="I76" t="n">
+        <v>88</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>34132.3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>6772.3</v>
+      </c>
+      <c r="F77" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.1115</v>
+      </c>
+      <c r="I77" t="n">
+        <v>89</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>34318.23</v>
+      </c>
+      <c r="E78" t="n">
+        <v>6809.2</v>
+      </c>
+      <c r="F78" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.1278</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.1121</v>
+      </c>
+      <c r="I78" t="n">
+        <v>92</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>32306.66</v>
+      </c>
+      <c r="E79" t="n">
+        <v>6410.1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="I79" t="n">
+        <v>92</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>14196.33</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2187.4</v>
+      </c>
+      <c r="F80" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="I80" t="n">
+        <v>89</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>13692.59</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2109.8</v>
+      </c>
+      <c r="F81" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="I81" t="n">
+        <v>92</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>14329.99</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2208</v>
+      </c>
+      <c r="F82" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="I82" t="n">
+        <v>89</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>15416.07</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3593.5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="I83" t="n">
+        <v>90</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>15890.79</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3704.1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="I84" t="n">
+        <v>89</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>15975.61</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3723.9</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="I85" t="n">
+        <v>92</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>14338.56</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3505.8</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="I86" t="n">
+        <v>88</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>13596.39</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3324.3</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="I87" t="n">
+        <v>88</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>14504.04</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3546.2</v>
+      </c>
+      <c r="F88" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="I88" t="n">
+        <v>90</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11890.94</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4262</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="I89" t="n">
+        <v>92</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11703.49</v>
+      </c>
+      <c r="E90" t="n">
+        <v>4194.8</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.0436</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="I90" t="n">
+        <v>92</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12206.57</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4375.1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="I91" t="n">
+        <v>91</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>34303.95</v>
+      </c>
+      <c r="E92" t="n">
+        <v>6806.3</v>
+      </c>
+      <c r="F92" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="I92" t="n">
+        <v>88</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>34311.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>6807.7</v>
+      </c>
+      <c r="F93" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="I93" t="n">
+        <v>91</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>33314.18</v>
+      </c>
+      <c r="E94" t="n">
+        <v>6610</v>
+      </c>
+      <c r="F94" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.1236</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="I94" t="n">
+        <v>93</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>13927.07</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2145.9</v>
+      </c>
+      <c r="F95" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="I95" t="n">
+        <v>89</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>14442.82</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2225.4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="I96" t="n">
+        <v>89</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>14318.03</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2206.2</v>
+      </c>
+      <c r="F97" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="I97" t="n">
+        <v>91</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>15532.08</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3620.5</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="I98" t="n">
+        <v>92</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>15181.63</v>
+      </c>
+      <c r="E99" t="n">
+        <v>3538.8</v>
+      </c>
+      <c r="F99" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.0563</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="I99" t="n">
+        <v>90</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>16000.46</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3729.7</v>
+      </c>
+      <c r="F100" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="I100" t="n">
+        <v>88</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>13770.13</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3366.8</v>
+      </c>
+      <c r="F101" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.0511</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="I101" t="n">
+        <v>88</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>14527.4</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3551.9</v>
+      </c>
+      <c r="F102" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="I102" t="n">
+        <v>89</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>13746</v>
+      </c>
+      <c r="E103" t="n">
+        <v>3360.9</v>
+      </c>
+      <c r="F103" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="I103" t="n">
+        <v>88</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11786.46</v>
+      </c>
+      <c r="E104" t="n">
+        <v>4224.5</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="I104" t="n">
+        <v>91</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>12475.17</v>
+      </c>
+      <c r="E105" t="n">
+        <v>4471.4</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="I105" t="n">
+        <v>88</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11816.14</v>
+      </c>
+      <c r="E106" t="n">
+        <v>4235.2</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="I106" t="n">
+        <v>90</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>33780.96</v>
+      </c>
+      <c r="E107" t="n">
+        <v>6702.6</v>
+      </c>
+      <c r="F107" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.1103</v>
+      </c>
+      <c r="I107" t="n">
+        <v>93</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>33479.86</v>
+      </c>
+      <c r="E108" t="n">
+        <v>6642.8</v>
+      </c>
+      <c r="F108" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.1093</v>
+      </c>
+      <c r="I108" t="n">
+        <v>87</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>32465.07</v>
+      </c>
+      <c r="E109" t="n">
+        <v>6441.5</v>
+      </c>
+      <c r="F109" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="I109" t="n">
+        <v>90</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>14479.13</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2231</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="I110" t="n">
+        <v>91</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>14378.81</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2215.5</v>
+      </c>
+      <c r="F111" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="I111" t="n">
+        <v>88</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>14405.47</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2219.6</v>
+      </c>
+      <c r="F112" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="I112" t="n">
+        <v>88</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>15227.56</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3549.5</v>
+      </c>
+      <c r="F113" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="I113" t="n">
+        <v>90</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>15218.39</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3547.4</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.0567</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="I114" t="n">
+        <v>92</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>16227.37</v>
+      </c>
+      <c r="E115" t="n">
+        <v>3782.6</v>
+      </c>
+      <c r="F115" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="I115" t="n">
+        <v>90</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>13921.87</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3403.9</v>
+      </c>
+      <c r="F116" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="I116" t="n">
+        <v>92</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>13813.36</v>
+      </c>
+      <c r="E117" t="n">
+        <v>3377.3</v>
+      </c>
+      <c r="F117" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="I117" t="n">
+        <v>91</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>14024.06</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3428.9</v>
+      </c>
+      <c r="F118" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.0523</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="I118" t="n">
+        <v>90</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>12311.59</v>
+      </c>
+      <c r="E119" t="n">
+        <v>4412.8</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="I119" t="n">
+        <v>91</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>12596.22</v>
+      </c>
+      <c r="E120" t="n">
+        <v>4514.8</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="I120" t="n">
+        <v>88</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11945.61</v>
+      </c>
+      <c r="E121" t="n">
+        <v>4281.6</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="I121" t="n">
+        <v>88</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>14557.76</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2314.4</v>
+      </c>
+      <c r="F122" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="I122" t="n">
+        <v>91</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>14520.75</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2308.5</v>
+      </c>
+      <c r="F123" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="I123" t="n">
+        <v>92</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>13880.57</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2206.8</v>
+      </c>
+      <c r="F124" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.0626</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="I124" t="n">
+        <v>88</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>16102.29</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2481.1</v>
+      </c>
+      <c r="F125" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="I125" t="n">
+        <v>88</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>16198.98</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2496</v>
+      </c>
+      <c r="F126" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="I126" t="n">
+        <v>90</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>16535.3</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2547.8</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.0512</v>
+      </c>
+      <c r="I127" t="n">
+        <v>88</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>16652.74</v>
+      </c>
+      <c r="E128" t="n">
+        <v>3881.8</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.0751</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="I128" t="n">
+        <v>92</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>16400.98</v>
+      </c>
+      <c r="E129" t="n">
+        <v>3823.1</v>
+      </c>
+      <c r="F129" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="I129" t="n">
+        <v>89</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>16350.26</v>
+      </c>
+      <c r="E130" t="n">
+        <v>3811.2</v>
+      </c>
+      <c r="F130" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.0766</v>
+      </c>
+      <c r="I130" t="n">
+        <v>88</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>14535.05</v>
+      </c>
+      <c r="E131" t="n">
+        <v>3553.8</v>
+      </c>
+      <c r="F131" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="I131" t="n">
+        <v>92</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>14799.47</v>
+      </c>
+      <c r="E132" t="n">
+        <v>3618.5</v>
+      </c>
+      <c r="F132" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="I132" t="n">
+        <v>88</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>15051.62</v>
+      </c>
+      <c r="E133" t="n">
+        <v>3680.1</v>
+      </c>
+      <c r="F133" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.0678</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="I133" t="n">
+        <v>89</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>12230.72</v>
+      </c>
+      <c r="E134" t="n">
+        <v>4383.8</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="I134" t="n">
+        <v>88</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>12028.36</v>
+      </c>
+      <c r="E135" t="n">
+        <v>4311.2</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="I135" t="n">
+        <v>88</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>12017.38</v>
+      </c>
+      <c r="E136" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.0866</v>
+      </c>
+      <c r="I136" t="n">
+        <v>88</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>14179.92</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2254.4</v>
+      </c>
+      <c r="F137" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="I137" t="n">
+        <v>90</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>14320.18</v>
+      </c>
+      <c r="E138" t="n">
+        <v>2276.7</v>
+      </c>
+      <c r="F138" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.0649</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="I138" t="n">
+        <v>88</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>14177.55</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2254</v>
+      </c>
+      <c r="F139" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="I139" t="n">
+        <v>89</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>16179.87</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2493</v>
+      </c>
+      <c r="F140" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.0733</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="I140" t="n">
+        <v>90</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>16294.97</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2510.8</v>
+      </c>
+      <c r="F141" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.0738</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="I141" t="n">
+        <v>88</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>15926.06</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2453.9</v>
+      </c>
+      <c r="F142" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="I142" t="n">
+        <v>92</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>16276.01</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3793.9</v>
+      </c>
+      <c r="F143" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.0738</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.0766</v>
+      </c>
+      <c r="I143" t="n">
+        <v>88</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>16522.48</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3851.4</v>
+      </c>
+      <c r="F144" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.07779999999999999</v>
+      </c>
+      <c r="I144" t="n">
+        <v>92</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>17012</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3965.5</v>
+      </c>
+      <c r="F145" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.0771</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.0801</v>
+      </c>
+      <c r="I145" t="n">
+        <v>88</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>15032.48</v>
+      </c>
+      <c r="E146" t="n">
+        <v>3675.4</v>
+      </c>
+      <c r="F146" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="I146" t="n">
+        <v>92</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>14087.73</v>
+      </c>
+      <c r="E147" t="n">
+        <v>3444.4</v>
+      </c>
+      <c r="F147" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="I147" t="n">
+        <v>92</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>14249.19</v>
+      </c>
+      <c r="E148" t="n">
+        <v>3483.9</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.0704</v>
+      </c>
+      <c r="I148" t="n">
+        <v>92</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>12017.46</v>
+      </c>
+      <c r="E149" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="I149" t="n">
+        <v>91</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>12029.88</v>
+      </c>
+      <c r="E150" t="n">
+        <v>4311.8</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="I150" t="n">
+        <v>91</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>12345.96</v>
+      </c>
+      <c r="E151" t="n">
+        <v>4425.1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="I151" t="n">
+        <v>91</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>15915.22</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2530.2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="I152" t="n">
+        <v>89</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>15112.61</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2402.6</v>
+      </c>
+      <c r="F153" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.0674</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="I153" t="n">
+        <v>89</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>15612.67</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2482.1</v>
+      </c>
+      <c r="F154" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.0697</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="I154" t="n">
+        <v>91</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>16081.03</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2477.8</v>
+      </c>
+      <c r="F155" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="I155" t="n">
+        <v>89</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>16522.24</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2545.8</v>
+      </c>
+      <c r="F156" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="I156" t="n">
+        <v>92</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>16014.95</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2467.6</v>
+      </c>
+      <c r="F157" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="I157" t="n">
+        <v>92</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>16364.67</v>
+      </c>
+      <c r="E158" t="n">
+        <v>3814.6</v>
+      </c>
+      <c r="F158" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="I158" t="n">
+        <v>90</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>16700.91</v>
+      </c>
+      <c r="E159" t="n">
+        <v>3893</v>
+      </c>
+      <c r="F159" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.0779</v>
+      </c>
+      <c r="I159" t="n">
+        <v>89</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>16207.92</v>
+      </c>
+      <c r="E160" t="n">
+        <v>3778.1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.0723</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="I160" t="n">
+        <v>90</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>14200.37</v>
+      </c>
+      <c r="E161" t="n">
+        <v>3472</v>
+      </c>
+      <c r="F161" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="I161" t="n">
+        <v>92</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>14595.87</v>
+      </c>
+      <c r="E162" t="n">
+        <v>3568.7</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="I162" t="n">
+        <v>91</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>14524.53</v>
+      </c>
+      <c r="E163" t="n">
+        <v>3551.2</v>
+      </c>
+      <c r="F163" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="I163" t="n">
+        <v>91</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>12013.36</v>
+      </c>
+      <c r="E164" t="n">
+        <v>4305.9</v>
+      </c>
+      <c r="F164" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="I164" t="n">
+        <v>90</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>12145.89</v>
+      </c>
+      <c r="E165" t="n">
+        <v>4353.4</v>
+      </c>
+      <c r="F165" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="I165" t="n">
+        <v>91</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>12144.79</v>
+      </c>
+      <c r="E166" t="n">
+        <v>4353</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="I166" t="n">
+        <v>89</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>16741.42</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2661.6</v>
+      </c>
+      <c r="F167" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.0733</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="I167" t="n">
+        <v>91</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>16041.4</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2550.3</v>
+      </c>
+      <c r="F168" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I168" t="n">
+        <v>92</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>16688.71</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2653.2</v>
+      </c>
+      <c r="F169" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="I169" t="n">
+        <v>89</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>16526.28</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2546.4</v>
+      </c>
+      <c r="F170" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.0723</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="I170" t="n">
+        <v>90</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>15589.99</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2402.2</v>
+      </c>
+      <c r="F171" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="I171" t="n">
+        <v>88</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>16209.73</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2497.6</v>
+      </c>
+      <c r="F172" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.0709</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="I172" t="n">
+        <v>91</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>15981.49</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3725.3</v>
+      </c>
+      <c r="F173" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.0731</v>
+      </c>
+      <c r="I173" t="n">
+        <v>88</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>16814.74</v>
+      </c>
+      <c r="E174" t="n">
+        <v>3919.5</v>
+      </c>
+      <c r="F174" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="I174" t="n">
+        <v>90</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>15967.48</v>
+      </c>
+      <c r="E175" t="n">
+        <v>3722</v>
+      </c>
+      <c r="F175" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="I175" t="n">
+        <v>90</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>15131.69</v>
+      </c>
+      <c r="E176" t="n">
+        <v>3699.7</v>
+      </c>
+      <c r="F176" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="I176" t="n">
+        <v>90</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>14197.61</v>
+      </c>
+      <c r="E177" t="n">
+        <v>3471.3</v>
+      </c>
+      <c r="F177" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="I177" t="n">
+        <v>90</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>15158.52</v>
+      </c>
+      <c r="E178" t="n">
+        <v>3706.2</v>
+      </c>
+      <c r="F178" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="I178" t="n">
+        <v>91</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>12571.49</v>
+      </c>
+      <c r="E179" t="n">
+        <v>4505.9</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.08840000000000001</v>
+      </c>
+      <c r="I179" t="n">
+        <v>91</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>12368</v>
+      </c>
+      <c r="E180" t="n">
+        <v>4433</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.0541</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="I180" t="n">
+        <v>90</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>12553.56</v>
+      </c>
+      <c r="E181" t="n">
+        <v>4499.5</v>
+      </c>
+      <c r="F181" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="I181" t="n">
+        <v>90</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>17894.24</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2844.9</v>
+      </c>
+      <c r="F182" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0.0786</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="I182" t="n">
+        <v>88</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>16771.29</v>
+      </c>
+      <c r="E183" t="n">
+        <v>2666.3</v>
+      </c>
+      <c r="F183" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="I183" t="n">
+        <v>92</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>16767.65</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2665.8</v>
+      </c>
+      <c r="F184" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="I184" t="n">
+        <v>90</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>14911.63</v>
+      </c>
+      <c r="E185" t="n">
+        <v>2297.6</v>
+      </c>
+      <c r="F185" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="I185" t="n">
+        <v>89</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>15614.98</v>
+      </c>
+      <c r="E186" t="n">
+        <v>2406</v>
+      </c>
+      <c r="F186" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="I186" t="n">
+        <v>91</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>15319.83</v>
+      </c>
+      <c r="E187" t="n">
+        <v>2360.5</v>
+      </c>
+      <c r="F187" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="I187" t="n">
+        <v>90</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>16878.97</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3934.5</v>
+      </c>
+      <c r="F188" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.0776</v>
+      </c>
+      <c r="I188" t="n">
+        <v>92</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>16742.75</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3902.7</v>
+      </c>
+      <c r="F189" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="I189" t="n">
+        <v>91</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>16296.68</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3798.8</v>
+      </c>
+      <c r="F190" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.0716</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="I190" t="n">
+        <v>90</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>15087.74</v>
+      </c>
+      <c r="E191" t="n">
+        <v>3688.9</v>
+      </c>
+      <c r="F191" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="I191" t="n">
+        <v>89</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>14928.84</v>
+      </c>
+      <c r="E192" t="n">
+        <v>3650.1</v>
+      </c>
+      <c r="F192" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="I192" t="n">
+        <v>92</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>14353.34</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3509.4</v>
+      </c>
+      <c r="F193" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="I193" t="n">
+        <v>91</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>12142.63</v>
+      </c>
+      <c r="E194" t="n">
+        <v>4352.2</v>
+      </c>
+      <c r="F194" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0.0859</v>
+      </c>
+      <c r="I194" t="n">
+        <v>92</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>12093.77</v>
+      </c>
+      <c r="E195" t="n">
+        <v>4334.7</v>
+      </c>
+      <c r="F195" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="I195" t="n">
+        <v>88</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>11939.75</v>
+      </c>
+      <c r="E196" t="n">
+        <v>4279.5</v>
+      </c>
+      <c r="F196" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.0844</v>
+      </c>
+      <c r="I196" t="n">
+        <v>92</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>17836.93</v>
+      </c>
+      <c r="E197" t="n">
+        <v>2835.8</v>
+      </c>
+      <c r="F197" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.07770000000000001</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="I197" t="n">
+        <v>92</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>17109.8</v>
+      </c>
+      <c r="E198" t="n">
+        <v>2720.2</v>
+      </c>
+      <c r="F198" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="I198" t="n">
+        <v>89</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>17768.02</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2824.8</v>
+      </c>
+      <c r="F199" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="I199" t="n">
+        <v>92</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>15649.81</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2411.4</v>
+      </c>
+      <c r="F200" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.0472</v>
+      </c>
+      <c r="I200" t="n">
+        <v>88</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>14818.61</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2283.3</v>
+      </c>
+      <c r="F201" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="I201" t="n">
+        <v>92</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>15363.89</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2367.3</v>
+      </c>
+      <c r="F202" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="I202" t="n">
+        <v>91</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>16946.46</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3950.2</v>
+      </c>
+      <c r="F203" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0.07729999999999999</v>
+      </c>
+      <c r="I203" t="n">
+        <v>91</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>16246.1</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3787</v>
+      </c>
+      <c r="F204" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="I204" t="n">
+        <v>88</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>16461.73</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3837.2</v>
+      </c>
+      <c r="F205" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0.0751</v>
+      </c>
+      <c r="I205" t="n">
+        <v>92</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>14554.27</v>
+      </c>
+      <c r="E206" t="n">
+        <v>3558.5</v>
+      </c>
+      <c r="F206" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="I206" t="n">
+        <v>88</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>14390.06</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3518.4</v>
+      </c>
+      <c r="F207" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0.0688</v>
+      </c>
+      <c r="I207" t="n">
+        <v>89</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>15111.22</v>
+      </c>
+      <c r="E208" t="n">
+        <v>3694.7</v>
+      </c>
+      <c r="F208" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0.0659</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0.0723</v>
+      </c>
+      <c r="I208" t="n">
+        <v>88</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>12552.25</v>
+      </c>
+      <c r="E209" t="n">
+        <v>4499</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="I209" t="n">
+        <v>91</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>11893.57</v>
+      </c>
+      <c r="E210" t="n">
+        <v>4262.9</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0.0518</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.0834</v>
+      </c>
+      <c r="I210" t="n">
+        <v>89</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>12764.13</v>
+      </c>
+      <c r="E211" t="n">
+        <v>4575</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0.0895</v>
+      </c>
+      <c r="I211" t="n">
+        <v>92</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>18039.16</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2867.9</v>
+      </c>
+      <c r="F212" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0.0786</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="I212" t="n">
+        <v>89</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>17155.31</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2727.4</v>
+      </c>
+      <c r="F213" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.0747</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="I213" t="n">
+        <v>88</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>17111.51</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2720.4</v>
+      </c>
+      <c r="F214" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="I214" t="n">
+        <v>90</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>14867.16</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2290.8</v>
+      </c>
+      <c r="F215" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="I215" t="n">
+        <v>91</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>15550.91</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2396.1</v>
+      </c>
+      <c r="F216" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0.0677</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="I216" t="n">
+        <v>91</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>15792.15</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2433.3</v>
+      </c>
+      <c r="F217" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0.0688</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="I217" t="n">
+        <v>92</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>16171.04</v>
+      </c>
+      <c r="E218" t="n">
+        <v>3769.5</v>
+      </c>
+      <c r="F218" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="I218" t="n">
+        <v>88</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>16978.18</v>
+      </c>
+      <c r="E219" t="n">
+        <v>3957.6</v>
+      </c>
+      <c r="F219" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="I219" t="n">
+        <v>91</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>15931.46</v>
+      </c>
+      <c r="E220" t="n">
+        <v>3713.6</v>
+      </c>
+      <c r="F220" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="I220" t="n">
+        <v>89</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>14973.8</v>
+      </c>
+      <c r="E221" t="n">
+        <v>3661.1</v>
+      </c>
+      <c r="F221" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0.0716</v>
+      </c>
+      <c r="I221" t="n">
+        <v>89</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>15122.16</v>
+      </c>
+      <c r="E222" t="n">
+        <v>3697.3</v>
+      </c>
+      <c r="F222" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0.0659</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.0723</v>
+      </c>
+      <c r="I222" t="n">
+        <v>91</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>14940.05</v>
+      </c>
+      <c r="E223" t="n">
+        <v>3652.8</v>
+      </c>
+      <c r="F223" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="I223" t="n">
+        <v>92</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>12470.57</v>
+      </c>
+      <c r="E224" t="n">
+        <v>4469.7</v>
+      </c>
+      <c r="F224" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0.08740000000000001</v>
+      </c>
+      <c r="I224" t="n">
+        <v>91</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>12607.92</v>
+      </c>
+      <c r="E225" t="n">
+        <v>4519</v>
+      </c>
+      <c r="F225" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.08840000000000001</v>
+      </c>
+      <c r="I225" t="n">
+        <v>88</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>11824.39</v>
+      </c>
+      <c r="E226" t="n">
+        <v>4238.1</v>
+      </c>
+      <c r="F226" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.0829</v>
+      </c>
+      <c r="I226" t="n">
+        <v>91</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
         <v>45766</v>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>CrestLine</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>CL-Premium 12ct</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>12744.58</v>
-      </c>
-      <c r="E65" t="n">
-        <v>326.8</v>
-      </c>
-      <c r="F65" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0.2151</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.2064</v>
-      </c>
-      <c r="I65" t="n">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>17164.13</v>
+      </c>
+      <c r="E227" t="n">
+        <v>2728.8</v>
+      </c>
+      <c r="F227" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="I227" t="n">
+        <v>91</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>18363.95</v>
+      </c>
+      <c r="E228" t="n">
+        <v>2919.5</v>
+      </c>
+      <c r="F228" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0.0799</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="I228" t="n">
+        <v>91</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>18115.14</v>
+      </c>
+      <c r="E229" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F229" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0.0788</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="I229" t="n">
+        <v>92</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>15017</v>
+      </c>
+      <c r="E230" t="n">
+        <v>2313.9</v>
+      </c>
+      <c r="F230" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0.0653</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="I230" t="n">
         <v>88</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>14916.58</v>
+      </c>
+      <c r="E231" t="n">
+        <v>2298.4</v>
+      </c>
+      <c r="F231" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0.0649</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="I231" t="n">
+        <v>90</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>15029.84</v>
+      </c>
+      <c r="E232" t="n">
+        <v>2315.8</v>
+      </c>
+      <c r="F232" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="I232" t="n">
+        <v>90</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>17150.77</v>
+      </c>
+      <c r="E233" t="n">
+        <v>3997.8</v>
+      </c>
+      <c r="F233" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="I233" t="n">
+        <v>90</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>16461.75</v>
+      </c>
+      <c r="E234" t="n">
+        <v>3837.2</v>
+      </c>
+      <c r="F234" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0.0716</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="I234" t="n">
+        <v>88</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>16891.86</v>
+      </c>
+      <c r="E235" t="n">
+        <v>3937.5</v>
+      </c>
+      <c r="F235" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="I235" t="n">
+        <v>88</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>14781.31</v>
+      </c>
+      <c r="E236" t="n">
+        <v>3614</v>
+      </c>
+      <c r="F236" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="I236" t="n">
+        <v>89</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>14706.45</v>
+      </c>
+      <c r="E237" t="n">
+        <v>3595.7</v>
+      </c>
+      <c r="F237" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="I237" t="n">
+        <v>89</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>14206.64</v>
+      </c>
+      <c r="E238" t="n">
+        <v>3473.5</v>
+      </c>
+      <c r="F238" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0.0618</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0.0678</v>
+      </c>
+      <c r="I238" t="n">
+        <v>90</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>12714.03</v>
+      </c>
+      <c r="E239" t="n">
+        <v>4557</v>
+      </c>
+      <c r="F239" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="I239" t="n">
+        <v>91</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>12080.9</v>
+      </c>
+      <c r="E240" t="n">
+        <v>4330.1</v>
+      </c>
+      <c r="F240" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0.08450000000000001</v>
+      </c>
+      <c r="I240" t="n">
+        <v>91</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>12352.62</v>
+      </c>
+      <c r="E241" t="n">
+        <v>4427.5</v>
+      </c>
+      <c r="F241" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="I241" t="n">
+        <v>90</v>
+      </c>
+      <c r="J241" t="n">
         <v>0</v>
       </c>
     </row>

--- a/stella/test_fixtures/strong_promo/iri_data.xlsx
+++ b/stella/test_fixtures/strong_promo/iri_data.xlsx
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17676.6</v>
+        <v>3213.93</v>
       </c>
       <c r="E2" t="n">
-        <v>2810.3</v>
+        <v>511</v>
       </c>
       <c r="F2" t="n">
         <v>6.29</v>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17212.92</v>
+        <v>3129.62</v>
       </c>
       <c r="E3" t="n">
-        <v>2736.6</v>
+        <v>497.6</v>
       </c>
       <c r="F3" t="n">
         <v>6.29</v>
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17793.73</v>
+        <v>3235.22</v>
       </c>
       <c r="E4" t="n">
-        <v>2828.9</v>
+        <v>514.3</v>
       </c>
       <c r="F4" t="n">
         <v>6.29</v>
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16316.37</v>
+        <v>2966.61</v>
       </c>
       <c r="E5" t="n">
-        <v>2514.1</v>
+        <v>457.1</v>
       </c>
       <c r="F5" t="n">
         <v>6.49</v>
@@ -643,10 +643,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15541.26</v>
+        <v>2825.68</v>
       </c>
       <c r="E6" t="n">
-        <v>2394.6</v>
+        <v>435.4</v>
       </c>
       <c r="F6" t="n">
         <v>6.49</v>
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16673.93</v>
+        <v>3031.62</v>
       </c>
       <c r="E7" t="n">
-        <v>2569.2</v>
+        <v>467.1</v>
       </c>
       <c r="F7" t="n">
         <v>6.49</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16861.55</v>
+        <v>3065.74</v>
       </c>
       <c r="E8" t="n">
-        <v>3930.4</v>
+        <v>714.6</v>
       </c>
       <c r="F8" t="n">
         <v>4.29</v>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16894.48</v>
+        <v>3071.72</v>
       </c>
       <c r="E9" t="n">
-        <v>3938.1</v>
+        <v>716</v>
       </c>
       <c r="F9" t="n">
         <v>4.29</v>
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16025.12</v>
+        <v>2913.66</v>
       </c>
       <c r="E10" t="n">
-        <v>3735.5</v>
+        <v>679.2</v>
       </c>
       <c r="F10" t="n">
         <v>4.29</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14563.71</v>
+        <v>2647.95</v>
       </c>
       <c r="E11" t="n">
-        <v>3560.8</v>
+        <v>647.4</v>
       </c>
       <c r="F11" t="n">
         <v>4.09</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14470.62</v>
+        <v>2631.02</v>
       </c>
       <c r="E12" t="n">
-        <v>3538</v>
+        <v>643.3</v>
       </c>
       <c r="F12" t="n">
         <v>4.09</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15120.95</v>
+        <v>2749.26</v>
       </c>
       <c r="E13" t="n">
-        <v>3697.1</v>
+        <v>672.2</v>
       </c>
       <c r="F13" t="n">
         <v>4.09</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12417.29</v>
+        <v>2257.69</v>
       </c>
       <c r="E14" t="n">
-        <v>4450.6</v>
+        <v>809.2</v>
       </c>
       <c r="F14" t="n">
         <v>2.79</v>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12592.98</v>
+        <v>2289.63</v>
       </c>
       <c r="E15" t="n">
-        <v>4513.6</v>
+        <v>820.7</v>
       </c>
       <c r="F15" t="n">
         <v>2.79</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12220.43</v>
+        <v>2221.9</v>
       </c>
       <c r="E16" t="n">
-        <v>4380.1</v>
+        <v>796.4</v>
       </c>
       <c r="F16" t="n">
         <v>2.79</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17636.2</v>
+        <v>3206.58</v>
       </c>
       <c r="E17" t="n">
-        <v>2803.8</v>
+        <v>509.8</v>
       </c>
       <c r="F17" t="n">
         <v>6.29</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17944.44</v>
+        <v>3262.63</v>
       </c>
       <c r="E18" t="n">
-        <v>2852.9</v>
+        <v>518.7</v>
       </c>
       <c r="F18" t="n">
         <v>6.29</v>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17056.48</v>
+        <v>3101.18</v>
       </c>
       <c r="E19" t="n">
-        <v>2711.7</v>
+        <v>493</v>
       </c>
       <c r="F19" t="n">
         <v>6.29</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15896.29</v>
+        <v>2890.23</v>
       </c>
       <c r="E20" t="n">
-        <v>2449.4</v>
+        <v>445.3</v>
       </c>
       <c r="F20" t="n">
         <v>6.49</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16023.63</v>
+        <v>2913.39</v>
       </c>
       <c r="E21" t="n">
-        <v>2469</v>
+        <v>448.9</v>
       </c>
       <c r="F21" t="n">
         <v>6.49</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15663.71</v>
+        <v>2847.95</v>
       </c>
       <c r="E22" t="n">
-        <v>2413.5</v>
+        <v>438.8</v>
       </c>
       <c r="F22" t="n">
         <v>6.49</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16027.51</v>
+        <v>2914.09</v>
       </c>
       <c r="E23" t="n">
-        <v>3736</v>
+        <v>679.3</v>
       </c>
       <c r="F23" t="n">
         <v>4.29</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16484.4</v>
+        <v>2997.16</v>
       </c>
       <c r="E24" t="n">
-        <v>3842.5</v>
+        <v>698.6</v>
       </c>
       <c r="F24" t="n">
         <v>4.29</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16155.66</v>
+        <v>2937.39</v>
       </c>
       <c r="E25" t="n">
-        <v>3765.9</v>
+        <v>684.7</v>
       </c>
       <c r="F25" t="n">
         <v>4.29</v>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14820.39</v>
+        <v>2694.62</v>
       </c>
       <c r="E26" t="n">
-        <v>3623.6</v>
+        <v>658.8</v>
       </c>
       <c r="F26" t="n">
         <v>4.09</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14548.23</v>
+        <v>2645.13</v>
       </c>
       <c r="E27" t="n">
-        <v>3557</v>
+        <v>646.7</v>
       </c>
       <c r="F27" t="n">
         <v>4.09</v>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15010.9</v>
+        <v>2729.25</v>
       </c>
       <c r="E28" t="n">
-        <v>3670.1</v>
+        <v>667.3</v>
       </c>
       <c r="F28" t="n">
         <v>4.09</v>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12472.68</v>
+        <v>2267.76</v>
       </c>
       <c r="E29" t="n">
-        <v>4470.5</v>
+        <v>812.8</v>
       </c>
       <c r="F29" t="n">
         <v>2.79</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12091.73</v>
+        <v>2198.5</v>
       </c>
       <c r="E30" t="n">
-        <v>4334</v>
+        <v>788</v>
       </c>
       <c r="F30" t="n">
         <v>2.79</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12602.31</v>
+        <v>2291.33</v>
       </c>
       <c r="E31" t="n">
-        <v>4517</v>
+        <v>821.3</v>
       </c>
       <c r="F31" t="n">
         <v>2.79</v>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17530.54</v>
+        <v>3187.37</v>
       </c>
       <c r="E32" t="n">
-        <v>2787</v>
+        <v>506.7</v>
       </c>
       <c r="F32" t="n">
         <v>6.29</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>17257.5</v>
+        <v>3137.73</v>
       </c>
       <c r="E33" t="n">
-        <v>2743.6</v>
+        <v>498.8</v>
       </c>
       <c r="F33" t="n">
         <v>6.29</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17387.77</v>
+        <v>3161.41</v>
       </c>
       <c r="E34" t="n">
-        <v>2764.4</v>
+        <v>502.6</v>
       </c>
       <c r="F34" t="n">
         <v>6.29</v>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16403.28</v>
+        <v>2982.41</v>
       </c>
       <c r="E35" t="n">
-        <v>2527.5</v>
+        <v>459.5</v>
       </c>
       <c r="F35" t="n">
         <v>6.49</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16235.87</v>
+        <v>2951.98</v>
       </c>
       <c r="E36" t="n">
-        <v>2501.7</v>
+        <v>454.8</v>
       </c>
       <c r="F36" t="n">
         <v>6.49</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16131.6</v>
+        <v>2933.02</v>
       </c>
       <c r="E37" t="n">
-        <v>2485.6</v>
+        <v>451.9</v>
       </c>
       <c r="F37" t="n">
         <v>6.49</v>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16594.73</v>
+        <v>3017.22</v>
       </c>
       <c r="E38" t="n">
-        <v>3868.2</v>
+        <v>703.3</v>
       </c>
       <c r="F38" t="n">
         <v>4.29</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16257.46</v>
+        <v>2955.9</v>
       </c>
       <c r="E39" t="n">
-        <v>3789.6</v>
+        <v>689</v>
       </c>
       <c r="F39" t="n">
         <v>4.29</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15896.56</v>
+        <v>2890.28</v>
       </c>
       <c r="E40" t="n">
-        <v>3705.5</v>
+        <v>673.7</v>
       </c>
       <c r="F40" t="n">
         <v>4.29</v>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14547.73</v>
+        <v>2645.04</v>
       </c>
       <c r="E41" t="n">
-        <v>3556.9</v>
+        <v>646.7</v>
       </c>
       <c r="F41" t="n">
         <v>4.09</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14287.89</v>
+        <v>2597.8</v>
       </c>
       <c r="E42" t="n">
-        <v>3493.4</v>
+        <v>635.2</v>
       </c>
       <c r="F42" t="n">
         <v>4.09</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14514.75</v>
+        <v>2639.05</v>
       </c>
       <c r="E43" t="n">
-        <v>3548.8</v>
+        <v>645.2</v>
       </c>
       <c r="F43" t="n">
         <v>4.09</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12623.07</v>
+        <v>2295.1</v>
       </c>
       <c r="E44" t="n">
-        <v>4524.4</v>
+        <v>822.6</v>
       </c>
       <c r="F44" t="n">
         <v>2.79</v>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12014.71</v>
+        <v>2184.49</v>
       </c>
       <c r="E45" t="n">
-        <v>4306.3</v>
+        <v>783</v>
       </c>
       <c r="F45" t="n">
         <v>2.79</v>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11842.22</v>
+        <v>2153.13</v>
       </c>
       <c r="E46" t="n">
-        <v>4244.5</v>
+        <v>771.7</v>
       </c>
       <c r="F46" t="n">
         <v>2.79</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>16816.37</v>
+        <v>3057.52</v>
       </c>
       <c r="E47" t="n">
-        <v>2673.5</v>
+        <v>486.1</v>
       </c>
       <c r="F47" t="n">
         <v>6.29</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17569.17</v>
+        <v>3194.39</v>
       </c>
       <c r="E48" t="n">
-        <v>2793.2</v>
+        <v>507.9</v>
       </c>
       <c r="F48" t="n">
         <v>6.29</v>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17222.99</v>
+        <v>3131.45</v>
       </c>
       <c r="E49" t="n">
-        <v>2738.2</v>
+        <v>497.8</v>
       </c>
       <c r="F49" t="n">
         <v>6.29</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15909.86</v>
+        <v>2892.7</v>
       </c>
       <c r="E50" t="n">
-        <v>2451.4</v>
+        <v>445.7</v>
       </c>
       <c r="F50" t="n">
         <v>6.49</v>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15807.69</v>
+        <v>2874.13</v>
       </c>
       <c r="E51" t="n">
-        <v>2435.7</v>
+        <v>442.9</v>
       </c>
       <c r="F51" t="n">
         <v>6.49</v>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16230.17</v>
+        <v>2950.94</v>
       </c>
       <c r="E52" t="n">
-        <v>2500.8</v>
+        <v>454.7</v>
       </c>
       <c r="F52" t="n">
         <v>6.49</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16333.91</v>
+        <v>2969.8</v>
       </c>
       <c r="E53" t="n">
-        <v>3807.4</v>
+        <v>692.3</v>
       </c>
       <c r="F53" t="n">
         <v>4.29</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15971.65</v>
+        <v>2903.94</v>
       </c>
       <c r="E54" t="n">
-        <v>3723</v>
+        <v>676.9</v>
       </c>
       <c r="F54" t="n">
         <v>4.29</v>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16011.76</v>
+        <v>2911.23</v>
       </c>
       <c r="E55" t="n">
-        <v>3732.3</v>
+        <v>678.6</v>
       </c>
       <c r="F55" t="n">
         <v>4.29</v>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15162.05</v>
+        <v>2756.74</v>
       </c>
       <c r="E56" t="n">
-        <v>3707.1</v>
+        <v>674</v>
       </c>
       <c r="F56" t="n">
         <v>4.09</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15099.68</v>
+        <v>2745.4</v>
       </c>
       <c r="E57" t="n">
-        <v>3691.9</v>
+        <v>671.2</v>
       </c>
       <c r="F57" t="n">
         <v>4.09</v>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14855.36</v>
+        <v>2700.97</v>
       </c>
       <c r="E58" t="n">
-        <v>3632.1</v>
+        <v>660.4</v>
       </c>
       <c r="F58" t="n">
         <v>4.09</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12046.07</v>
+        <v>2190.19</v>
       </c>
       <c r="E59" t="n">
-        <v>4317.6</v>
+        <v>785</v>
       </c>
       <c r="F59" t="n">
         <v>2.79</v>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12736.77</v>
+        <v>2315.78</v>
       </c>
       <c r="E60" t="n">
-        <v>4565.2</v>
+        <v>830</v>
       </c>
       <c r="F60" t="n">
         <v>2.79</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12549.76</v>
+        <v>2281.77</v>
       </c>
       <c r="E61" t="n">
-        <v>4498.1</v>
+        <v>817.8</v>
       </c>
       <c r="F61" t="n">
         <v>2.79</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>33487.79</v>
+        <v>6088.69</v>
       </c>
       <c r="E62" t="n">
-        <v>6644.4</v>
+        <v>1208.1</v>
       </c>
       <c r="F62" t="n">
         <v>5.04</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>33662.76</v>
+        <v>6120.5</v>
       </c>
       <c r="E63" t="n">
-        <v>6679.1</v>
+        <v>1214.4</v>
       </c>
       <c r="F63" t="n">
         <v>5.04</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>32158.16</v>
+        <v>5846.94</v>
       </c>
       <c r="E64" t="n">
-        <v>6380.6</v>
+        <v>1160.1</v>
       </c>
       <c r="F64" t="n">
         <v>5.04</v>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14040.01</v>
+        <v>2552.73</v>
       </c>
       <c r="E65" t="n">
-        <v>2163.3</v>
+        <v>393.3</v>
       </c>
       <c r="F65" t="n">
         <v>6.49</v>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13616.87</v>
+        <v>2475.79</v>
       </c>
       <c r="E66" t="n">
-        <v>2098.1</v>
+        <v>381.5</v>
       </c>
       <c r="F66" t="n">
         <v>6.49</v>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14128.42</v>
+        <v>2568.8</v>
       </c>
       <c r="E67" t="n">
-        <v>2177</v>
+        <v>395.8</v>
       </c>
       <c r="F67" t="n">
         <v>6.49</v>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15477.11</v>
+        <v>2814.02</v>
       </c>
       <c r="E68" t="n">
-        <v>3607.7</v>
+        <v>655.9</v>
       </c>
       <c r="F68" t="n">
         <v>4.29</v>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>15244.46</v>
+        <v>2771.72</v>
       </c>
       <c r="E69" t="n">
-        <v>3553.5</v>
+        <v>646.1</v>
       </c>
       <c r="F69" t="n">
         <v>4.29</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>15192.84</v>
+        <v>2762.34</v>
       </c>
       <c r="E70" t="n">
-        <v>3541.5</v>
+        <v>643.9</v>
       </c>
       <c r="F70" t="n">
         <v>4.29</v>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>14135.3</v>
+        <v>2570.05</v>
       </c>
       <c r="E71" t="n">
-        <v>3456.1</v>
+        <v>628.4</v>
       </c>
       <c r="F71" t="n">
         <v>4.09</v>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13666.97</v>
+        <v>2484.9</v>
       </c>
       <c r="E72" t="n">
-        <v>3341.6</v>
+        <v>607.6</v>
       </c>
       <c r="F72" t="n">
         <v>4.09</v>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14514.27</v>
+        <v>2638.96</v>
       </c>
       <c r="E73" t="n">
-        <v>3548.7</v>
+        <v>645.2</v>
       </c>
       <c r="F73" t="n">
         <v>4.09</v>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12232.05</v>
+        <v>2224.01</v>
       </c>
       <c r="E74" t="n">
-        <v>4384.2</v>
+        <v>797.1</v>
       </c>
       <c r="F74" t="n">
         <v>2.79</v>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12004.36</v>
+        <v>2182.61</v>
       </c>
       <c r="E75" t="n">
-        <v>4302.6</v>
+        <v>782.3</v>
       </c>
       <c r="F75" t="n">
         <v>2.79</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12241.63</v>
+        <v>2225.75</v>
       </c>
       <c r="E76" t="n">
-        <v>4387.7</v>
+        <v>797.8</v>
       </c>
       <c r="F76" t="n">
         <v>2.79</v>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>34132.3</v>
+        <v>6205.87</v>
       </c>
       <c r="E77" t="n">
-        <v>6772.3</v>
+        <v>1231.3</v>
       </c>
       <c r="F77" t="n">
         <v>5.04</v>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>34318.23</v>
+        <v>6239.68</v>
       </c>
       <c r="E78" t="n">
-        <v>6809.2</v>
+        <v>1238</v>
       </c>
       <c r="F78" t="n">
         <v>5.04</v>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>32306.66</v>
+        <v>5873.94</v>
       </c>
       <c r="E79" t="n">
-        <v>6410.1</v>
+        <v>1165.5</v>
       </c>
       <c r="F79" t="n">
         <v>5.04</v>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14196.33</v>
+        <v>2581.15</v>
       </c>
       <c r="E80" t="n">
-        <v>2187.4</v>
+        <v>397.7</v>
       </c>
       <c r="F80" t="n">
         <v>6.49</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13692.59</v>
+        <v>2489.56</v>
       </c>
       <c r="E81" t="n">
-        <v>2109.8</v>
+        <v>383.6</v>
       </c>
       <c r="F81" t="n">
         <v>6.49</v>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>14329.99</v>
+        <v>2605.45</v>
       </c>
       <c r="E82" t="n">
-        <v>2208</v>
+        <v>401.5</v>
       </c>
       <c r="F82" t="n">
         <v>6.49</v>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>15416.07</v>
+        <v>2802.92</v>
       </c>
       <c r="E83" t="n">
-        <v>3593.5</v>
+        <v>653.4</v>
       </c>
       <c r="F83" t="n">
         <v>4.29</v>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>15890.79</v>
+        <v>2889.23</v>
       </c>
       <c r="E84" t="n">
-        <v>3704.1</v>
+        <v>673.5</v>
       </c>
       <c r="F84" t="n">
         <v>4.29</v>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>15975.61</v>
+        <v>2904.66</v>
       </c>
       <c r="E85" t="n">
-        <v>3723.9</v>
+        <v>677.1</v>
       </c>
       <c r="F85" t="n">
         <v>4.29</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>14338.56</v>
+        <v>2607.01</v>
       </c>
       <c r="E86" t="n">
-        <v>3505.8</v>
+        <v>637.4</v>
       </c>
       <c r="F86" t="n">
         <v>4.09</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13596.39</v>
+        <v>2472.07</v>
       </c>
       <c r="E87" t="n">
-        <v>3324.3</v>
+        <v>604.4</v>
       </c>
       <c r="F87" t="n">
         <v>4.09</v>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>14504.04</v>
+        <v>2637.1</v>
       </c>
       <c r="E88" t="n">
-        <v>3546.2</v>
+        <v>644.8</v>
       </c>
       <c r="F88" t="n">
         <v>4.09</v>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11890.94</v>
+        <v>2161.99</v>
       </c>
       <c r="E89" t="n">
-        <v>4262</v>
+        <v>774.9</v>
       </c>
       <c r="F89" t="n">
         <v>2.79</v>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11703.49</v>
+        <v>2127.91</v>
       </c>
       <c r="E90" t="n">
-        <v>4194.8</v>
+        <v>762.7</v>
       </c>
       <c r="F90" t="n">
         <v>2.79</v>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12206.57</v>
+        <v>2219.38</v>
       </c>
       <c r="E91" t="n">
-        <v>4375.1</v>
+        <v>795.5</v>
       </c>
       <c r="F91" t="n">
         <v>2.79</v>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>34303.95</v>
+        <v>6237.08</v>
       </c>
       <c r="E92" t="n">
-        <v>6806.3</v>
+        <v>1237.5</v>
       </c>
       <c r="F92" t="n">
         <v>5.04</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>34311.01</v>
+        <v>6238.37</v>
       </c>
       <c r="E93" t="n">
-        <v>6807.7</v>
+        <v>1237.8</v>
       </c>
       <c r="F93" t="n">
         <v>5.04</v>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>33314.18</v>
+        <v>6057.12</v>
       </c>
       <c r="E94" t="n">
-        <v>6610</v>
+        <v>1201.8</v>
       </c>
       <c r="F94" t="n">
         <v>5.04</v>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13927.07</v>
+        <v>2532.19</v>
       </c>
       <c r="E95" t="n">
-        <v>2145.9</v>
+        <v>390.2</v>
       </c>
       <c r="F95" t="n">
         <v>6.49</v>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>14442.82</v>
+        <v>2625.97</v>
       </c>
       <c r="E96" t="n">
-        <v>2225.4</v>
+        <v>404.6</v>
       </c>
       <c r="F96" t="n">
         <v>6.49</v>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>14318.03</v>
+        <v>2603.28</v>
       </c>
       <c r="E97" t="n">
-        <v>2206.2</v>
+        <v>401.1</v>
       </c>
       <c r="F97" t="n">
         <v>6.49</v>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>15532.08</v>
+        <v>2824.02</v>
       </c>
       <c r="E98" t="n">
-        <v>3620.5</v>
+        <v>658.3</v>
       </c>
       <c r="F98" t="n">
         <v>4.29</v>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>15181.63</v>
+        <v>2760.3</v>
       </c>
       <c r="E99" t="n">
-        <v>3538.8</v>
+        <v>643.4</v>
       </c>
       <c r="F99" t="n">
         <v>4.29</v>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>16000.46</v>
+        <v>2909.17</v>
       </c>
       <c r="E100" t="n">
-        <v>3729.7</v>
+        <v>678.1</v>
       </c>
       <c r="F100" t="n">
         <v>4.29</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>13770.13</v>
+        <v>2503.66</v>
       </c>
       <c r="E101" t="n">
-        <v>3366.8</v>
+        <v>612.1</v>
       </c>
       <c r="F101" t="n">
         <v>4.09</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>14527.4</v>
+        <v>2641.35</v>
       </c>
       <c r="E102" t="n">
-        <v>3551.9</v>
+        <v>645.8</v>
       </c>
       <c r="F102" t="n">
         <v>4.09</v>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>13746</v>
+        <v>2499.27</v>
       </c>
       <c r="E103" t="n">
-        <v>3360.9</v>
+        <v>611.1</v>
       </c>
       <c r="F103" t="n">
         <v>4.09</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11786.46</v>
+        <v>2142.99</v>
       </c>
       <c r="E104" t="n">
-        <v>4224.5</v>
+        <v>768.1</v>
       </c>
       <c r="F104" t="n">
         <v>2.79</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12475.17</v>
+        <v>2268.21</v>
       </c>
       <c r="E105" t="n">
-        <v>4471.4</v>
+        <v>813</v>
       </c>
       <c r="F105" t="n">
         <v>2.79</v>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11816.14</v>
+        <v>2148.39</v>
       </c>
       <c r="E106" t="n">
-        <v>4235.2</v>
+        <v>770</v>
       </c>
       <c r="F106" t="n">
         <v>2.79</v>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>33780.96</v>
+        <v>6141.99</v>
       </c>
       <c r="E107" t="n">
-        <v>6702.6</v>
+        <v>1218.6</v>
       </c>
       <c r="F107" t="n">
         <v>5.04</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>33479.86</v>
+        <v>6087.25</v>
       </c>
       <c r="E108" t="n">
-        <v>6642.8</v>
+        <v>1207.8</v>
       </c>
       <c r="F108" t="n">
         <v>5.04</v>
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>32465.07</v>
+        <v>5902.74</v>
       </c>
       <c r="E109" t="n">
-        <v>6441.5</v>
+        <v>1171.2</v>
       </c>
       <c r="F109" t="n">
         <v>5.04</v>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>14479.13</v>
+        <v>2632.57</v>
       </c>
       <c r="E110" t="n">
-        <v>2231</v>
+        <v>405.6</v>
       </c>
       <c r="F110" t="n">
         <v>6.49</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>14378.81</v>
+        <v>2614.33</v>
       </c>
       <c r="E111" t="n">
-        <v>2215.5</v>
+        <v>402.8</v>
       </c>
       <c r="F111" t="n">
         <v>6.49</v>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>14405.47</v>
+        <v>2619.18</v>
       </c>
       <c r="E112" t="n">
-        <v>2219.6</v>
+        <v>403.6</v>
       </c>
       <c r="F112" t="n">
         <v>6.49</v>
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>15227.56</v>
+        <v>2768.65</v>
       </c>
       <c r="E113" t="n">
-        <v>3549.5</v>
+        <v>645.4</v>
       </c>
       <c r="F113" t="n">
         <v>4.29</v>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>15218.39</v>
+        <v>2766.98</v>
       </c>
       <c r="E114" t="n">
-        <v>3547.4</v>
+        <v>645</v>
       </c>
       <c r="F114" t="n">
         <v>4.29</v>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>16227.37</v>
+        <v>2950.43</v>
       </c>
       <c r="E115" t="n">
-        <v>3782.6</v>
+        <v>687.7</v>
       </c>
       <c r="F115" t="n">
         <v>4.29</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>13921.87</v>
+        <v>2531.25</v>
       </c>
       <c r="E116" t="n">
-        <v>3403.9</v>
+        <v>618.9</v>
       </c>
       <c r="F116" t="n">
         <v>4.09</v>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>13813.36</v>
+        <v>2511.52</v>
       </c>
       <c r="E117" t="n">
-        <v>3377.3</v>
+        <v>614.1</v>
       </c>
       <c r="F117" t="n">
         <v>4.09</v>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>14024.06</v>
+        <v>2549.83</v>
       </c>
       <c r="E118" t="n">
-        <v>3428.9</v>
+        <v>623.4</v>
       </c>
       <c r="F118" t="n">
         <v>4.09</v>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>12311.59</v>
+        <v>2238.47</v>
       </c>
       <c r="E119" t="n">
-        <v>4412.8</v>
+        <v>802.3</v>
       </c>
       <c r="F119" t="n">
         <v>2.79</v>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>12596.22</v>
+        <v>2290.22</v>
       </c>
       <c r="E120" t="n">
-        <v>4514.8</v>
+        <v>820.9</v>
       </c>
       <c r="F120" t="n">
         <v>2.79</v>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11945.61</v>
+        <v>2171.93</v>
       </c>
       <c r="E121" t="n">
-        <v>4281.6</v>
+        <v>778.5</v>
       </c>
       <c r="F121" t="n">
         <v>2.79</v>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>14557.76</v>
+        <v>2646.87</v>
       </c>
       <c r="E122" t="n">
-        <v>2314.4</v>
+        <v>420.8</v>
       </c>
       <c r="F122" t="n">
         <v>6.29</v>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>14520.75</v>
+        <v>2640.14</v>
       </c>
       <c r="E123" t="n">
-        <v>2308.5</v>
+        <v>419.7</v>
       </c>
       <c r="F123" t="n">
         <v>6.29</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>13880.57</v>
+        <v>2523.74</v>
       </c>
       <c r="E124" t="n">
-        <v>2206.8</v>
+        <v>401.2</v>
       </c>
       <c r="F124" t="n">
         <v>6.29</v>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>16102.29</v>
+        <v>2927.69</v>
       </c>
       <c r="E125" t="n">
-        <v>2481.1</v>
+        <v>451.1</v>
       </c>
       <c r="F125" t="n">
         <v>6.49</v>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>16198.98</v>
+        <v>2945.27</v>
       </c>
       <c r="E126" t="n">
-        <v>2496</v>
+        <v>453.8</v>
       </c>
       <c r="F126" t="n">
         <v>6.49</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>16535.3</v>
+        <v>3006.42</v>
       </c>
       <c r="E127" t="n">
-        <v>2547.8</v>
+        <v>463.2</v>
       </c>
       <c r="F127" t="n">
         <v>6.49</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>16652.74</v>
+        <v>3027.77</v>
       </c>
       <c r="E128" t="n">
-        <v>3881.8</v>
+        <v>705.8</v>
       </c>
       <c r="F128" t="n">
         <v>4.29</v>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>16400.98</v>
+        <v>2982</v>
       </c>
       <c r="E129" t="n">
-        <v>3823.1</v>
+        <v>695.1</v>
       </c>
       <c r="F129" t="n">
         <v>4.29</v>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>16350.26</v>
+        <v>2972.77</v>
       </c>
       <c r="E130" t="n">
-        <v>3811.2</v>
+        <v>693</v>
       </c>
       <c r="F130" t="n">
         <v>4.29</v>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>14535.05</v>
+        <v>2642.74</v>
       </c>
       <c r="E131" t="n">
-        <v>3553.8</v>
+        <v>646.1</v>
       </c>
       <c r="F131" t="n">
         <v>4.09</v>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>14799.47</v>
+        <v>2690.81</v>
       </c>
       <c r="E132" t="n">
-        <v>3618.5</v>
+        <v>657.9</v>
       </c>
       <c r="F132" t="n">
         <v>4.09</v>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>15051.62</v>
+        <v>2736.66</v>
       </c>
       <c r="E133" t="n">
-        <v>3680.1</v>
+        <v>669.1</v>
       </c>
       <c r="F133" t="n">
         <v>4.09</v>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>12230.72</v>
+        <v>2223.77</v>
       </c>
       <c r="E134" t="n">
-        <v>4383.8</v>
+        <v>797</v>
       </c>
       <c r="F134" t="n">
         <v>2.79</v>
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>12028.36</v>
+        <v>2186.97</v>
       </c>
       <c r="E135" t="n">
-        <v>4311.2</v>
+        <v>783.9</v>
       </c>
       <c r="F135" t="n">
         <v>2.79</v>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>12017.38</v>
+        <v>2184.98</v>
       </c>
       <c r="E136" t="n">
-        <v>4307.3</v>
+        <v>783.1</v>
       </c>
       <c r="F136" t="n">
         <v>2.79</v>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>14179.92</v>
+        <v>2578.17</v>
       </c>
       <c r="E137" t="n">
-        <v>2254.4</v>
+        <v>409.9</v>
       </c>
       <c r="F137" t="n">
         <v>6.29</v>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>14320.18</v>
+        <v>2603.67</v>
       </c>
       <c r="E138" t="n">
-        <v>2276.7</v>
+        <v>413.9</v>
       </c>
       <c r="F138" t="n">
         <v>6.29</v>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>14177.55</v>
+        <v>2577.74</v>
       </c>
       <c r="E139" t="n">
-        <v>2254</v>
+        <v>409.8</v>
       </c>
       <c r="F139" t="n">
         <v>6.29</v>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>16179.87</v>
+        <v>2941.79</v>
       </c>
       <c r="E140" t="n">
-        <v>2493</v>
+        <v>453.3</v>
       </c>
       <c r="F140" t="n">
         <v>6.49</v>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>16294.97</v>
+        <v>2962.72</v>
       </c>
       <c r="E141" t="n">
-        <v>2510.8</v>
+        <v>456.5</v>
       </c>
       <c r="F141" t="n">
         <v>6.49</v>
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>15926.06</v>
+        <v>2895.65</v>
       </c>
       <c r="E142" t="n">
-        <v>2453.9</v>
+        <v>446.2</v>
       </c>
       <c r="F142" t="n">
         <v>6.49</v>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>16276.01</v>
+        <v>2959.27</v>
       </c>
       <c r="E143" t="n">
-        <v>3793.9</v>
+        <v>689.8</v>
       </c>
       <c r="F143" t="n">
         <v>4.29</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>16522.48</v>
+        <v>3004.09</v>
       </c>
       <c r="E144" t="n">
-        <v>3851.4</v>
+        <v>700.3</v>
       </c>
       <c r="F144" t="n">
         <v>4.29</v>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>17012</v>
+        <v>3093.09</v>
       </c>
       <c r="E145" t="n">
-        <v>3965.5</v>
+        <v>721</v>
       </c>
       <c r="F145" t="n">
         <v>4.29</v>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>15032.48</v>
+        <v>2733.18</v>
       </c>
       <c r="E146" t="n">
-        <v>3675.4</v>
+        <v>668.3</v>
       </c>
       <c r="F146" t="n">
         <v>4.09</v>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>14087.73</v>
+        <v>2561.41</v>
       </c>
       <c r="E147" t="n">
-        <v>3444.4</v>
+        <v>626.3</v>
       </c>
       <c r="F147" t="n">
         <v>4.09</v>
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>14249.19</v>
+        <v>2590.76</v>
       </c>
       <c r="E148" t="n">
-        <v>3483.9</v>
+        <v>633.4</v>
       </c>
       <c r="F148" t="n">
         <v>4.09</v>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>12017.46</v>
+        <v>2184.99</v>
       </c>
       <c r="E149" t="n">
-        <v>4307.3</v>
+        <v>783.2</v>
       </c>
       <c r="F149" t="n">
         <v>2.79</v>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>12029.88</v>
+        <v>2187.25</v>
       </c>
       <c r="E150" t="n">
-        <v>4311.8</v>
+        <v>784</v>
       </c>
       <c r="F150" t="n">
         <v>2.79</v>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>12345.96</v>
+        <v>2244.72</v>
       </c>
       <c r="E151" t="n">
-        <v>4425.1</v>
+        <v>804.6</v>
       </c>
       <c r="F151" t="n">
         <v>2.79</v>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>15915.22</v>
+        <v>2893.68</v>
       </c>
       <c r="E152" t="n">
-        <v>2530.2</v>
+        <v>460</v>
       </c>
       <c r="F152" t="n">
         <v>6.29</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>15112.61</v>
+        <v>2747.75</v>
       </c>
       <c r="E153" t="n">
-        <v>2402.6</v>
+        <v>436.8</v>
       </c>
       <c r="F153" t="n">
         <v>6.29</v>
@@ -5971,10 +5971,10 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>15612.67</v>
+        <v>2838.67</v>
       </c>
       <c r="E154" t="n">
-        <v>2482.1</v>
+        <v>451.3</v>
       </c>
       <c r="F154" t="n">
         <v>6.29</v>
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>16081.03</v>
+        <v>2923.82</v>
       </c>
       <c r="E155" t="n">
-        <v>2477.8</v>
+        <v>450.5</v>
       </c>
       <c r="F155" t="n">
         <v>6.49</v>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>16522.24</v>
+        <v>3004.04</v>
       </c>
       <c r="E156" t="n">
-        <v>2545.8</v>
+        <v>462.9</v>
       </c>
       <c r="F156" t="n">
         <v>6.49</v>
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>16014.95</v>
+        <v>2911.81</v>
       </c>
       <c r="E157" t="n">
-        <v>2467.6</v>
+        <v>448.7</v>
       </c>
       <c r="F157" t="n">
         <v>6.49</v>
@@ -6115,10 +6115,10 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>16364.67</v>
+        <v>2975.39</v>
       </c>
       <c r="E158" t="n">
-        <v>3814.6</v>
+        <v>693.6</v>
       </c>
       <c r="F158" t="n">
         <v>4.29</v>
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>16700.91</v>
+        <v>3036.53</v>
       </c>
       <c r="E159" t="n">
-        <v>3893</v>
+        <v>707.8</v>
       </c>
       <c r="F159" t="n">
         <v>4.29</v>
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>16207.92</v>
+        <v>2946.9</v>
       </c>
       <c r="E160" t="n">
-        <v>3778.1</v>
+        <v>686.9</v>
       </c>
       <c r="F160" t="n">
         <v>4.29</v>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>14200.37</v>
+        <v>2581.89</v>
       </c>
       <c r="E161" t="n">
-        <v>3472</v>
+        <v>631.3</v>
       </c>
       <c r="F161" t="n">
         <v>4.09</v>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>14595.87</v>
+        <v>2653.79</v>
       </c>
       <c r="E162" t="n">
-        <v>3568.7</v>
+        <v>648.8</v>
       </c>
       <c r="F162" t="n">
         <v>4.09</v>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>14524.53</v>
+        <v>2640.82</v>
       </c>
       <c r="E163" t="n">
-        <v>3551.2</v>
+        <v>645.7</v>
       </c>
       <c r="F163" t="n">
         <v>4.09</v>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>12013.36</v>
+        <v>2184.25</v>
       </c>
       <c r="E164" t="n">
-        <v>4305.9</v>
+        <v>782.9</v>
       </c>
       <c r="F164" t="n">
         <v>2.79</v>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>12145.89</v>
+        <v>2208.34</v>
       </c>
       <c r="E165" t="n">
-        <v>4353.4</v>
+        <v>791.5</v>
       </c>
       <c r="F165" t="n">
         <v>2.79</v>
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>12144.79</v>
+        <v>2208.14</v>
       </c>
       <c r="E166" t="n">
-        <v>4353</v>
+        <v>791.4</v>
       </c>
       <c r="F166" t="n">
         <v>2.79</v>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>16741.42</v>
+        <v>3043.89</v>
       </c>
       <c r="E167" t="n">
-        <v>2661.6</v>
+        <v>483.9</v>
       </c>
       <c r="F167" t="n">
         <v>6.29</v>
@@ -6475,10 +6475,10 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>16041.4</v>
+        <v>2916.62</v>
       </c>
       <c r="E168" t="n">
-        <v>2550.3</v>
+        <v>463.7</v>
       </c>
       <c r="F168" t="n">
         <v>6.29</v>
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>16688.71</v>
+        <v>3034.31</v>
       </c>
       <c r="E169" t="n">
-        <v>2653.2</v>
+        <v>482.4</v>
       </c>
       <c r="F169" t="n">
         <v>6.29</v>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>16526.28</v>
+        <v>3004.78</v>
       </c>
       <c r="E170" t="n">
-        <v>2546.4</v>
+        <v>463</v>
       </c>
       <c r="F170" t="n">
         <v>6.49</v>
@@ -6583,10 +6583,10 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>15589.99</v>
+        <v>2834.54</v>
       </c>
       <c r="E171" t="n">
-        <v>2402.2</v>
+        <v>436.8</v>
       </c>
       <c r="F171" t="n">
         <v>6.49</v>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>16209.73</v>
+        <v>2947.22</v>
       </c>
       <c r="E172" t="n">
-        <v>2497.6</v>
+        <v>454.1</v>
       </c>
       <c r="F172" t="n">
         <v>6.49</v>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>15981.49</v>
+        <v>2905.73</v>
       </c>
       <c r="E173" t="n">
-        <v>3725.3</v>
+        <v>677.3</v>
       </c>
       <c r="F173" t="n">
         <v>4.29</v>
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>16814.74</v>
+        <v>3057.23</v>
       </c>
       <c r="E174" t="n">
-        <v>3919.5</v>
+        <v>712.6</v>
       </c>
       <c r="F174" t="n">
         <v>4.29</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>15967.48</v>
+        <v>2903.18</v>
       </c>
       <c r="E175" t="n">
-        <v>3722</v>
+        <v>676.7</v>
       </c>
       <c r="F175" t="n">
         <v>4.29</v>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>15131.69</v>
+        <v>2751.22</v>
       </c>
       <c r="E176" t="n">
-        <v>3699.7</v>
+        <v>672.7</v>
       </c>
       <c r="F176" t="n">
         <v>4.09</v>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>14197.61</v>
+        <v>2581.38</v>
       </c>
       <c r="E177" t="n">
-        <v>3471.3</v>
+        <v>631.1</v>
       </c>
       <c r="F177" t="n">
         <v>4.09</v>
@@ -6835,10 +6835,10 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>15158.52</v>
+        <v>2756.09</v>
       </c>
       <c r="E178" t="n">
-        <v>3706.2</v>
+        <v>673.9</v>
       </c>
       <c r="F178" t="n">
         <v>4.09</v>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>12571.49</v>
+        <v>2285.73</v>
       </c>
       <c r="E179" t="n">
-        <v>4505.9</v>
+        <v>819.3</v>
       </c>
       <c r="F179" t="n">
         <v>2.79</v>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>12368</v>
+        <v>2248.73</v>
       </c>
       <c r="E180" t="n">
-        <v>4433</v>
+        <v>806</v>
       </c>
       <c r="F180" t="n">
         <v>2.79</v>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>12553.56</v>
+        <v>2282.47</v>
       </c>
       <c r="E181" t="n">
-        <v>4499.5</v>
+        <v>818.1</v>
       </c>
       <c r="F181" t="n">
         <v>2.79</v>
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>17894.24</v>
+        <v>3253.5</v>
       </c>
       <c r="E182" t="n">
-        <v>2844.9</v>
+        <v>517.2</v>
       </c>
       <c r="F182" t="n">
         <v>6.29</v>
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>16771.29</v>
+        <v>3049.32</v>
       </c>
       <c r="E183" t="n">
-        <v>2666.3</v>
+        <v>484.8</v>
       </c>
       <c r="F183" t="n">
         <v>6.29</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>16767.65</v>
+        <v>3048.66</v>
       </c>
       <c r="E184" t="n">
-        <v>2665.8</v>
+        <v>484.7</v>
       </c>
       <c r="F184" t="n">
         <v>6.29</v>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>14911.63</v>
+        <v>2711.21</v>
       </c>
       <c r="E185" t="n">
-        <v>2297.6</v>
+        <v>417.8</v>
       </c>
       <c r="F185" t="n">
         <v>6.49</v>
@@ -7123,10 +7123,10 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>15614.98</v>
+        <v>2839.09</v>
       </c>
       <c r="E186" t="n">
-        <v>2406</v>
+        <v>437.5</v>
       </c>
       <c r="F186" t="n">
         <v>6.49</v>
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>15319.83</v>
+        <v>2785.42</v>
       </c>
       <c r="E187" t="n">
-        <v>2360.5</v>
+        <v>429.2</v>
       </c>
       <c r="F187" t="n">
         <v>6.49</v>
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>16878.97</v>
+        <v>3068.9</v>
       </c>
       <c r="E188" t="n">
-        <v>3934.5</v>
+        <v>715.4</v>
       </c>
       <c r="F188" t="n">
         <v>4.29</v>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>16742.75</v>
+        <v>3044.14</v>
       </c>
       <c r="E189" t="n">
-        <v>3902.7</v>
+        <v>709.6</v>
       </c>
       <c r="F189" t="n">
         <v>4.29</v>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>16296.68</v>
+        <v>2963.03</v>
       </c>
       <c r="E190" t="n">
-        <v>3798.8</v>
+        <v>690.7</v>
       </c>
       <c r="F190" t="n">
         <v>4.29</v>
@@ -7303,10 +7303,10 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>15087.74</v>
+        <v>2743.22</v>
       </c>
       <c r="E191" t="n">
-        <v>3688.9</v>
+        <v>670.7</v>
       </c>
       <c r="F191" t="n">
         <v>4.09</v>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>14928.84</v>
+        <v>2714.34</v>
       </c>
       <c r="E192" t="n">
-        <v>3650.1</v>
+        <v>663.7</v>
       </c>
       <c r="F192" t="n">
         <v>4.09</v>
@@ -7375,10 +7375,10 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>14353.34</v>
+        <v>2609.7</v>
       </c>
       <c r="E193" t="n">
-        <v>3509.4</v>
+        <v>638.1</v>
       </c>
       <c r="F193" t="n">
         <v>4.09</v>
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>12142.63</v>
+        <v>2207.75</v>
       </c>
       <c r="E194" t="n">
-        <v>4352.2</v>
+        <v>791.3</v>
       </c>
       <c r="F194" t="n">
         <v>2.79</v>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>12093.77</v>
+        <v>2198.87</v>
       </c>
       <c r="E195" t="n">
-        <v>4334.7</v>
+        <v>788.1</v>
       </c>
       <c r="F195" t="n">
         <v>2.79</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>11939.75</v>
+        <v>2170.86</v>
       </c>
       <c r="E196" t="n">
-        <v>4279.5</v>
+        <v>778.1</v>
       </c>
       <c r="F196" t="n">
         <v>2.79</v>
@@ -7519,10 +7519,10 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>17836.93</v>
+        <v>3243.08</v>
       </c>
       <c r="E197" t="n">
-        <v>2835.8</v>
+        <v>515.6</v>
       </c>
       <c r="F197" t="n">
         <v>6.29</v>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>17109.8</v>
+        <v>3110.87</v>
       </c>
       <c r="E198" t="n">
-        <v>2720.2</v>
+        <v>494.6</v>
       </c>
       <c r="F198" t="n">
         <v>6.29</v>
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>17768.02</v>
+        <v>3230.55</v>
       </c>
       <c r="E199" t="n">
-        <v>2824.8</v>
+        <v>513.6</v>
       </c>
       <c r="F199" t="n">
         <v>6.29</v>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>15649.81</v>
+        <v>2845.42</v>
       </c>
       <c r="E200" t="n">
-        <v>2411.4</v>
+        <v>438.4</v>
       </c>
       <c r="F200" t="n">
         <v>6.49</v>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>14818.61</v>
+        <v>2694.29</v>
       </c>
       <c r="E201" t="n">
-        <v>2283.3</v>
+        <v>415.1</v>
       </c>
       <c r="F201" t="n">
         <v>6.49</v>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>15363.89</v>
+        <v>2793.43</v>
       </c>
       <c r="E202" t="n">
-        <v>2367.3</v>
+        <v>430.4</v>
       </c>
       <c r="F202" t="n">
         <v>6.49</v>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>16946.46</v>
+        <v>3081.17</v>
       </c>
       <c r="E203" t="n">
-        <v>3950.2</v>
+        <v>718.2</v>
       </c>
       <c r="F203" t="n">
         <v>4.29</v>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>16246.1</v>
+        <v>2953.84</v>
       </c>
       <c r="E204" t="n">
-        <v>3787</v>
+        <v>688.5</v>
       </c>
       <c r="F204" t="n">
         <v>4.29</v>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>16461.73</v>
+        <v>2993.04</v>
       </c>
       <c r="E205" t="n">
-        <v>3837.2</v>
+        <v>697.7</v>
       </c>
       <c r="F205" t="n">
         <v>4.29</v>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>14554.27</v>
+        <v>2646.23</v>
       </c>
       <c r="E206" t="n">
-        <v>3558.5</v>
+        <v>647</v>
       </c>
       <c r="F206" t="n">
         <v>4.09</v>
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>14390.06</v>
+        <v>2616.37</v>
       </c>
       <c r="E207" t="n">
-        <v>3518.4</v>
+        <v>639.7</v>
       </c>
       <c r="F207" t="n">
         <v>4.09</v>
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>15111.22</v>
+        <v>2747.49</v>
       </c>
       <c r="E208" t="n">
-        <v>3694.7</v>
+        <v>671.8</v>
       </c>
       <c r="F208" t="n">
         <v>4.09</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>12552.25</v>
+        <v>2282.23</v>
       </c>
       <c r="E209" t="n">
-        <v>4499</v>
+        <v>818</v>
       </c>
       <c r="F209" t="n">
         <v>2.79</v>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>11893.57</v>
+        <v>2162.47</v>
       </c>
       <c r="E210" t="n">
-        <v>4262.9</v>
+        <v>775.1</v>
       </c>
       <c r="F210" t="n">
         <v>2.79</v>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>12764.13</v>
+        <v>2320.75</v>
       </c>
       <c r="E211" t="n">
-        <v>4575</v>
+        <v>831.8</v>
       </c>
       <c r="F211" t="n">
         <v>2.79</v>
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>18039.16</v>
+        <v>3279.85</v>
       </c>
       <c r="E212" t="n">
-        <v>2867.9</v>
+        <v>521.4</v>
       </c>
       <c r="F212" t="n">
         <v>6.29</v>
@@ -8095,10 +8095,10 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>17155.31</v>
+        <v>3119.15</v>
       </c>
       <c r="E213" t="n">
-        <v>2727.4</v>
+        <v>495.9</v>
       </c>
       <c r="F213" t="n">
         <v>6.29</v>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>17111.51</v>
+        <v>3111.18</v>
       </c>
       <c r="E214" t="n">
-        <v>2720.4</v>
+        <v>494.6</v>
       </c>
       <c r="F214" t="n">
         <v>6.29</v>
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>14867.16</v>
+        <v>2703.12</v>
       </c>
       <c r="E215" t="n">
-        <v>2290.8</v>
+        <v>416.5</v>
       </c>
       <c r="F215" t="n">
         <v>6.49</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>15550.91</v>
+        <v>2827.44</v>
       </c>
       <c r="E216" t="n">
-        <v>2396.1</v>
+        <v>435.7</v>
       </c>
       <c r="F216" t="n">
         <v>6.49</v>
@@ -8239,10 +8239,10 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>15792.15</v>
+        <v>2871.3</v>
       </c>
       <c r="E217" t="n">
-        <v>2433.3</v>
+        <v>442.4</v>
       </c>
       <c r="F217" t="n">
         <v>6.49</v>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>16171.04</v>
+        <v>2940.19</v>
       </c>
       <c r="E218" t="n">
-        <v>3769.5</v>
+        <v>685.4</v>
       </c>
       <c r="F218" t="n">
         <v>4.29</v>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>16978.18</v>
+        <v>3086.94</v>
       </c>
       <c r="E219" t="n">
-        <v>3957.6</v>
+        <v>719.6</v>
       </c>
       <c r="F219" t="n">
         <v>4.29</v>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>15931.46</v>
+        <v>2896.63</v>
       </c>
       <c r="E220" t="n">
-        <v>3713.6</v>
+        <v>675.2</v>
       </c>
       <c r="F220" t="n">
         <v>4.29</v>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>14973.8</v>
+        <v>2722.51</v>
       </c>
       <c r="E221" t="n">
-        <v>3661.1</v>
+        <v>665.7</v>
       </c>
       <c r="F221" t="n">
         <v>4.09</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>15122.16</v>
+        <v>2749.48</v>
       </c>
       <c r="E222" t="n">
-        <v>3697.3</v>
+        <v>672.2</v>
       </c>
       <c r="F222" t="n">
         <v>4.09</v>
@@ -8455,10 +8455,10 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>14940.05</v>
+        <v>2716.37</v>
       </c>
       <c r="E223" t="n">
-        <v>3652.8</v>
+        <v>664.1</v>
       </c>
       <c r="F223" t="n">
         <v>4.09</v>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>12470.57</v>
+        <v>2267.38</v>
       </c>
       <c r="E224" t="n">
-        <v>4469.7</v>
+        <v>812.7</v>
       </c>
       <c r="F224" t="n">
         <v>2.79</v>
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>12607.92</v>
+        <v>2292.35</v>
       </c>
       <c r="E225" t="n">
-        <v>4519</v>
+        <v>821.6</v>
       </c>
       <c r="F225" t="n">
         <v>2.79</v>
@@ -8563,10 +8563,10 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>11824.39</v>
+        <v>2149.89</v>
       </c>
       <c r="E226" t="n">
-        <v>4238.1</v>
+        <v>770.6</v>
       </c>
       <c r="F226" t="n">
         <v>2.79</v>
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>17164.13</v>
+        <v>3120.75</v>
       </c>
       <c r="E227" t="n">
-        <v>2728.8</v>
+        <v>496.1</v>
       </c>
       <c r="F227" t="n">
         <v>6.29</v>
@@ -8635,10 +8635,10 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>18363.95</v>
+        <v>3338.9</v>
       </c>
       <c r="E228" t="n">
-        <v>2919.5</v>
+        <v>530.8</v>
       </c>
       <c r="F228" t="n">
         <v>6.29</v>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>18115.14</v>
+        <v>3293.66</v>
       </c>
       <c r="E229" t="n">
-        <v>2880</v>
+        <v>523.6</v>
       </c>
       <c r="F229" t="n">
         <v>6.29</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>15017</v>
+        <v>2730.36</v>
       </c>
       <c r="E230" t="n">
-        <v>2313.9</v>
+        <v>420.7</v>
       </c>
       <c r="F230" t="n">
         <v>6.49</v>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>14916.58</v>
+        <v>2712.11</v>
       </c>
       <c r="E231" t="n">
-        <v>2298.4</v>
+        <v>417.9</v>
       </c>
       <c r="F231" t="n">
         <v>6.49</v>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>15029.84</v>
+        <v>2732.7</v>
       </c>
       <c r="E232" t="n">
-        <v>2315.8</v>
+        <v>421.1</v>
       </c>
       <c r="F232" t="n">
         <v>6.49</v>
@@ -8815,10 +8815,10 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>17150.77</v>
+        <v>3118.32</v>
       </c>
       <c r="E233" t="n">
-        <v>3997.8</v>
+        <v>726.9</v>
       </c>
       <c r="F233" t="n">
         <v>4.29</v>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>16461.75</v>
+        <v>2993.04</v>
       </c>
       <c r="E234" t="n">
-        <v>3837.2</v>
+        <v>697.7</v>
       </c>
       <c r="F234" t="n">
         <v>4.29</v>
@@ -8887,10 +8887,10 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>16891.86</v>
+        <v>3071.25</v>
       </c>
       <c r="E235" t="n">
-        <v>3937.5</v>
+        <v>715.9</v>
       </c>
       <c r="F235" t="n">
         <v>4.29</v>
@@ -8923,10 +8923,10 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>14781.31</v>
+        <v>2687.51</v>
       </c>
       <c r="E236" t="n">
-        <v>3614</v>
+        <v>657.1</v>
       </c>
       <c r="F236" t="n">
         <v>4.09</v>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>14706.45</v>
+        <v>2673.9</v>
       </c>
       <c r="E237" t="n">
-        <v>3595.7</v>
+        <v>653.8</v>
       </c>
       <c r="F237" t="n">
         <v>4.09</v>
@@ -8995,10 +8995,10 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>14206.64</v>
+        <v>2583.03</v>
       </c>
       <c r="E238" t="n">
-        <v>3473.5</v>
+        <v>631.5</v>
       </c>
       <c r="F238" t="n">
         <v>4.09</v>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>12714.03</v>
+        <v>2311.64</v>
       </c>
       <c r="E239" t="n">
-        <v>4557</v>
+        <v>828.5</v>
       </c>
       <c r="F239" t="n">
         <v>2.79</v>
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>12080.9</v>
+        <v>2196.53</v>
       </c>
       <c r="E240" t="n">
-        <v>4330.1</v>
+        <v>787.3</v>
       </c>
       <c r="F240" t="n">
         <v>2.79</v>
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>12352.62</v>
+        <v>2245.93</v>
       </c>
       <c r="E241" t="n">
-        <v>4427.5</v>
+        <v>805</v>
       </c>
       <c r="F241" t="n">
         <v>2.79</v>

--- a/stella/test_fixtures/strong_promo/iri_data.xlsx
+++ b/stella/test_fixtures/strong_promo/iri_data.xlsx
@@ -508,10 +508,10 @@
         <v>6.29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0761</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0545</v>
+        <v>0.0539</v>
       </c>
       <c r="I2" t="n">
         <v>89</v>
@@ -544,10 +544,10 @@
         <v>6.29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0741</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.053</v>
+        <v>0.0536</v>
       </c>
       <c r="I3" t="n">
         <v>90</v>
@@ -580,10 +580,10 @@
         <v>6.29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0766</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0548</v>
+        <v>0.054</v>
       </c>
       <c r="I4" t="n">
         <v>88</v>
@@ -616,10 +616,10 @@
         <v>6.49</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0702</v>
+        <v>0.0698</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0487</v>
+        <v>0.0484</v>
       </c>
       <c r="I5" t="n">
         <v>92</v>
@@ -652,10 +652,10 @@
         <v>6.49</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0669</v>
+        <v>0.0692</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0464</v>
+        <v>0.048</v>
       </c>
       <c r="I6" t="n">
         <v>91</v>
@@ -688,10 +688,10 @@
         <v>6.49</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0718</v>
+        <v>0.0701</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0498</v>
+        <v>0.0486</v>
       </c>
       <c r="I7" t="n">
         <v>91</v>
@@ -724,10 +724,10 @@
         <v>4.29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0726</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0762</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>89</v>
@@ -760,10 +760,10 @@
         <v>4.29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0727</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0755</v>
       </c>
       <c r="I9" t="n">
         <v>92</v>
@@ -796,10 +796,10 @@
         <v>4.29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0712</v>
       </c>
       <c r="H10" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0747</v>
       </c>
       <c r="I10" t="n">
         <v>92</v>
@@ -832,10 +832,10 @@
         <v>4.09</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0633</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="I11" t="n">
         <v>91</v>
@@ -868,10 +868,10 @@
         <v>4.09</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0623</v>
+        <v>0.0633</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0697</v>
       </c>
       <c r="I12" t="n">
         <v>89</v>
@@ -904,10 +904,10 @@
         <v>4.09</v>
       </c>
       <c r="G13" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0638</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0717</v>
+        <v>0.0702</v>
       </c>
       <c r="I13" t="n">
         <v>90</v>
@@ -940,10 +940,10 @@
         <v>2.79</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0534</v>
+        <v>0.0533</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0863</v>
+        <v>0.0861</v>
       </c>
       <c r="I14" t="n">
         <v>88</v>
@@ -976,10 +976,10 @@
         <v>2.79</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0542</v>
+        <v>0.0535</v>
       </c>
       <c r="H15" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0863</v>
       </c>
       <c r="I15" t="n">
         <v>88</v>
@@ -1012,10 +1012,10 @@
         <v>2.79</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0526</v>
+        <v>0.0532</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0849</v>
+        <v>0.0858</v>
       </c>
       <c r="I16" t="n">
         <v>91</v>
@@ -1048,10 +1048,10 @@
         <v>6.29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0765</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0547</v>
+        <v>0.0539</v>
       </c>
       <c r="I17" t="n">
         <v>91</v>
@@ -1084,10 +1084,10 @@
         <v>6.29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0779</v>
+        <v>0.0756</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0557</v>
+        <v>0.0541</v>
       </c>
       <c r="I18" t="n">
         <v>89</v>
@@ -1120,10 +1120,10 @@
         <v>6.29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.074</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0529</v>
+        <v>0.0536</v>
       </c>
       <c r="I19" t="n">
         <v>89</v>
@@ -1156,10 +1156,10 @@
         <v>6.49</v>
       </c>
       <c r="G20" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0478</v>
+        <v>0.0483</v>
       </c>
       <c r="I20" t="n">
         <v>91</v>
@@ -1192,10 +1192,10 @@
         <v>6.49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0482</v>
+        <v>0.0484</v>
       </c>
       <c r="I21" t="n">
         <v>88</v>
@@ -1228,10 +1228,10 @@
         <v>6.49</v>
       </c>
       <c r="G22" t="n">
-        <v>0.068</v>
+        <v>0.0694</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0471</v>
+        <v>0.0482</v>
       </c>
       <c r="I22" t="n">
         <v>89</v>
@@ -1264,10 +1264,10 @@
         <v>4.29</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0696</v>
+        <v>0.0713</v>
       </c>
       <c r="H23" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>88</v>
@@ -1300,10 +1300,10 @@
         <v>4.29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0717</v>
       </c>
       <c r="H24" t="n">
-        <v>0.075</v>
+        <v>0.0752</v>
       </c>
       <c r="I24" t="n">
         <v>91</v>
@@ -1336,10 +1336,10 @@
         <v>4.29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0701</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0735</v>
+        <v>0.075</v>
       </c>
       <c r="I25" t="n">
         <v>91</v>
@@ -1372,10 +1372,10 @@
         <v>4.09</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0643</v>
+        <v>0.0636</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0707</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>91</v>
@@ -1408,10 +1408,10 @@
         <v>4.09</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0631</v>
+        <v>0.0634</v>
       </c>
       <c r="H27" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0698</v>
       </c>
       <c r="I27" t="n">
         <v>91</v>
@@ -1444,10 +1444,10 @@
         <v>4.09</v>
       </c>
       <c r="G28" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0638</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0717</v>
+        <v>0.0702</v>
       </c>
       <c r="I28" t="n">
         <v>90</v>
@@ -1480,10 +1480,10 @@
         <v>2.79</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0541</v>
+        <v>0.0534</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0873</v>
+        <v>0.0863</v>
       </c>
       <c r="I29" t="n">
         <v>90</v>
@@ -1516,10 +1516,10 @@
         <v>2.79</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0525</v>
+        <v>0.0531</v>
       </c>
       <c r="H30" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0858</v>
       </c>
       <c r="I30" t="n">
         <v>88</v>
@@ -1552,10 +1552,10 @@
         <v>2.79</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0547</v>
+        <v>0.0536</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0882</v>
+        <v>0.0864</v>
       </c>
       <c r="I31" t="n">
         <v>88</v>
@@ -1588,10 +1588,10 @@
         <v>6.29</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0764</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0548</v>
+        <v>0.054</v>
       </c>
       <c r="I32" t="n">
         <v>89</v>
@@ -1624,10 +1624,10 @@
         <v>6.29</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0752</v>
+        <v>0.0751</v>
       </c>
       <c r="H33" t="n">
-        <v>0.054</v>
+        <v>0.0538</v>
       </c>
       <c r="I33" t="n">
         <v>89</v>
@@ -1660,10 +1660,10 @@
         <v>6.29</v>
       </c>
       <c r="G34" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0752</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0544</v>
+        <v>0.0539</v>
       </c>
       <c r="I34" t="n">
         <v>91</v>
@@ -1696,10 +1696,10 @@
         <v>6.49</v>
       </c>
       <c r="G35" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0701</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0497</v>
+        <v>0.0486</v>
       </c>
       <c r="I35" t="n">
         <v>90</v>
@@ -1732,10 +1732,10 @@
         <v>6.49</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0707</v>
+        <v>0.0699</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0492</v>
+        <v>0.0485</v>
       </c>
       <c r="I36" t="n">
         <v>91</v>
@@ -1768,10 +1768,10 @@
         <v>6.49</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0703</v>
+        <v>0.0698</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0489</v>
+        <v>0.0485</v>
       </c>
       <c r="I37" t="n">
         <v>91</v>
@@ -1804,10 +1804,10 @@
         <v>4.29</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0723</v>
+        <v>0.0718</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0761</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="I38" t="n">
         <v>90</v>
@@ -1840,10 +1840,10 @@
         <v>4.29</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0708</v>
+        <v>0.0716</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0745</v>
+        <v>0.0751</v>
       </c>
       <c r="I39" t="n">
         <v>92</v>
@@ -1876,10 +1876,10 @@
         <v>4.29</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0693</v>
+        <v>0.0713</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I40" t="n">
         <v>88</v>
@@ -1912,10 +1912,10 @@
         <v>4.09</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0634</v>
+        <v>0.0635</v>
       </c>
       <c r="H41" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0699</v>
       </c>
       <c r="I41" t="n">
         <v>88</v>
@@ -1948,10 +1948,10 @@
         <v>4.09</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0622</v>
+        <v>0.0633</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0687</v>
+        <v>0.0697</v>
       </c>
       <c r="I42" t="n">
         <v>88</v>
@@ -1984,10 +1984,10 @@
         <v>4.09</v>
       </c>
       <c r="G43" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0698</v>
+        <v>0.0699</v>
       </c>
       <c r="I43" t="n">
         <v>91</v>
@@ -2020,10 +2020,10 @@
         <v>2.79</v>
       </c>
       <c r="G44" t="n">
-        <v>0.055</v>
+        <v>0.0536</v>
       </c>
       <c r="H44" t="n">
-        <v>0.089</v>
+        <v>0.0866</v>
       </c>
       <c r="I44" t="n">
         <v>90</v>
@@ -2056,10 +2056,10 @@
         <v>2.79</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0523</v>
+        <v>0.0531</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0847</v>
+        <v>0.0858</v>
       </c>
       <c r="I45" t="n">
         <v>88</v>
@@ -2092,10 +2092,10 @@
         <v>2.79</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0516</v>
+        <v>0.053</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0835</v>
+        <v>0.0856</v>
       </c>
       <c r="I46" t="n">
         <v>90</v>
@@ -2128,10 +2128,10 @@
         <v>6.29</v>
       </c>
       <c r="G47" t="n">
-        <v>0.073</v>
+        <v>0.0747</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0521</v>
+        <v>0.0535</v>
       </c>
       <c r="I47" t="n">
         <v>91</v>
@@ -2164,10 +2164,10 @@
         <v>6.29</v>
       </c>
       <c r="G48" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0545</v>
+        <v>0.0539</v>
       </c>
       <c r="I48" t="n">
         <v>90</v>
@@ -2200,10 +2200,10 @@
         <v>6.29</v>
       </c>
       <c r="G49" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0534</v>
+        <v>0.0537</v>
       </c>
       <c r="I49" t="n">
         <v>89</v>
@@ -2236,10 +2236,10 @@
         <v>6.49</v>
       </c>
       <c r="G50" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0696</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0478</v>
+        <v>0.0483</v>
       </c>
       <c r="I50" t="n">
         <v>88</v>
@@ -2272,10 +2272,10 @@
         <v>6.49</v>
       </c>
       <c r="G51" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0475</v>
+        <v>0.0482</v>
       </c>
       <c r="I51" t="n">
         <v>92</v>
@@ -2308,10 +2308,10 @@
         <v>6.49</v>
       </c>
       <c r="G52" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0699</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0488</v>
+        <v>0.0485</v>
       </c>
       <c r="I52" t="n">
         <v>90</v>
@@ -2344,10 +2344,10 @@
         <v>4.29</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0709</v>
+        <v>0.0716</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0743</v>
+        <v>0.0751</v>
       </c>
       <c r="I53" t="n">
         <v>89</v>
@@ -2380,10 +2380,10 @@
         <v>4.29</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0693</v>
+        <v>0.0713</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0726</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I54" t="n">
         <v>89</v>
@@ -2416,10 +2416,10 @@
         <v>4.29</v>
       </c>
       <c r="G55" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0728</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I55" t="n">
         <v>90</v>
@@ -2452,10 +2452,10 @@
         <v>4.09</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0658</v>
+        <v>0.0639</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0723</v>
+        <v>0.0703</v>
       </c>
       <c r="I56" t="n">
         <v>88</v>
@@ -2488,10 +2488,10 @@
         <v>4.09</v>
       </c>
       <c r="G57" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0639</v>
       </c>
       <c r="H57" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0703</v>
       </c>
       <c r="I57" t="n">
         <v>92</v>
@@ -2524,10 +2524,10 @@
         <v>4.09</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0645</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0708</v>
+        <v>0.0701</v>
       </c>
       <c r="I58" t="n">
         <v>91</v>
@@ -2560,10 +2560,10 @@
         <v>2.79</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0523</v>
+        <v>0.0531</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0842</v>
+        <v>0.0857</v>
       </c>
       <c r="I59" t="n">
         <v>91</v>
@@ -2596,10 +2596,10 @@
         <v>2.79</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0553</v>
+        <v>0.0537</v>
       </c>
       <c r="H60" t="n">
-        <v>0.089</v>
+        <v>0.0866</v>
       </c>
       <c r="I60" t="n">
         <v>90</v>
@@ -2632,10 +2632,10 @@
         <v>2.79</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0545</v>
+        <v>0.0535</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0877</v>
+        <v>0.0863</v>
       </c>
       <c r="I61" t="n">
         <v>91</v>
@@ -2668,10 +2668,10 @@
         <v>5.04</v>
       </c>
       <c r="G62" t="n">
-        <v>0.126</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1103</v>
+        <v>0.0655</v>
       </c>
       <c r="I62" t="n">
         <v>87</v>
@@ -2704,10 +2704,10 @@
         <v>5.04</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1266</v>
+        <v>0.0856</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1108</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="I63" t="n">
         <v>93</v>
@@ -2740,10 +2740,10 @@
         <v>5.04</v>
       </c>
       <c r="G64" t="n">
-        <v>0.121</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1059</v>
+        <v>0.0646</v>
       </c>
       <c r="I64" t="n">
         <v>90</v>
@@ -2776,10 +2776,10 @@
         <v>6.49</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0528</v>
+        <v>0.0663</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0359</v>
+        <v>0.0458</v>
       </c>
       <c r="I65" t="n">
         <v>91</v>
@@ -2812,10 +2812,10 @@
         <v>6.49</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0512</v>
+        <v>0.066</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0348</v>
+        <v>0.0456</v>
       </c>
       <c r="I66" t="n">
         <v>88</v>
@@ -2848,10 +2848,10 @@
         <v>6.49</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0532</v>
+        <v>0.0664</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0361</v>
+        <v>0.0458</v>
       </c>
       <c r="I67" t="n">
         <v>90</v>
@@ -2884,10 +2884,10 @@
         <v>4.29</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0582</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0599</v>
+        <v>0.0721</v>
       </c>
       <c r="I68" t="n">
         <v>90</v>
@@ -2920,10 +2920,10 @@
         <v>4.29</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0574</v>
+        <v>0.0688</v>
       </c>
       <c r="H69" t="n">
-        <v>0.059</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="I69" t="n">
         <v>92</v>
@@ -2956,10 +2956,10 @@
         <v>4.29</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0572</v>
+        <v>0.0687</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0588</v>
+        <v>0.0718</v>
       </c>
       <c r="I70" t="n">
         <v>90</v>
@@ -2992,10 +2992,10 @@
         <v>4.09</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0532</v>
+        <v>0.0614</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0573</v>
+        <v>0.0673</v>
       </c>
       <c r="I71" t="n">
         <v>90</v>
@@ -3028,10 +3028,10 @@
         <v>4.09</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0514</v>
+        <v>0.061</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0554</v>
+        <v>0.0669</v>
       </c>
       <c r="I72" t="n">
         <v>89</v>
@@ -3064,10 +3064,10 @@
         <v>4.09</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0546</v>
+        <v>0.0617</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0589</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="I73" t="n">
         <v>89</v>
@@ -3100,10 +3100,10 @@
         <v>2.79</v>
       </c>
       <c r="G74" t="n">
-        <v>0.046</v>
+        <v>0.0518</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0727</v>
+        <v>0.0833</v>
       </c>
       <c r="I74" t="n">
         <v>90</v>
@@ -3136,10 +3136,10 @@
         <v>2.79</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0452</v>
+        <v>0.0516</v>
       </c>
       <c r="H75" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="I75" t="n">
         <v>90</v>
@@ -3172,10 +3172,10 @@
         <v>2.79</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0461</v>
+        <v>0.0518</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0728</v>
+        <v>0.0833</v>
       </c>
       <c r="I76" t="n">
         <v>88</v>
@@ -3208,10 +3208,10 @@
         <v>5.04</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1271</v>
+        <v>0.0858</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1115</v>
+        <v>0.0658</v>
       </c>
       <c r="I77" t="n">
         <v>89</v>
@@ -3244,10 +3244,10 @@
         <v>5.04</v>
       </c>
       <c r="G78" t="n">
-        <v>0.1278</v>
+        <v>0.0859</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1121</v>
+        <v>0.0659</v>
       </c>
       <c r="I78" t="n">
         <v>92</v>
@@ -3280,10 +3280,10 @@
         <v>5.04</v>
       </c>
       <c r="G79" t="n">
-        <v>0.1203</v>
+        <v>0.0844</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1056</v>
+        <v>0.0646</v>
       </c>
       <c r="I79" t="n">
         <v>92</v>
@@ -3316,10 +3316,10 @@
         <v>6.49</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0529</v>
+        <v>0.0663</v>
       </c>
       <c r="H80" t="n">
-        <v>0.036</v>
+        <v>0.0458</v>
       </c>
       <c r="I80" t="n">
         <v>89</v>
@@ -3352,10 +3352,10 @@
         <v>6.49</v>
       </c>
       <c r="G81" t="n">
-        <v>0.051</v>
+        <v>0.0659</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0347</v>
+        <v>0.0455</v>
       </c>
       <c r="I81" t="n">
         <v>92</v>
@@ -3388,10 +3388,10 @@
         <v>6.49</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0534</v>
+        <v>0.0664</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0364</v>
+        <v>0.0459</v>
       </c>
       <c r="I82" t="n">
         <v>89</v>
@@ -3424,10 +3424,10 @@
         <v>4.29</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0574</v>
+        <v>0.0688</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0592</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="I83" t="n">
         <v>90</v>
@@ -3460,10 +3460,10 @@
         <v>4.29</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0592</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>0.061</v>
+        <v>0.0723</v>
       </c>
       <c r="I84" t="n">
         <v>89</v>
@@ -3496,10 +3496,10 @@
         <v>4.29</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0595</v>
+        <v>0.0692</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0613</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="I85" t="n">
         <v>92</v>
@@ -3532,10 +3532,10 @@
         <v>4.09</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0534</v>
+        <v>0.0614</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0577</v>
+        <v>0.0674</v>
       </c>
       <c r="I86" t="n">
         <v>88</v>
@@ -3568,10 +3568,10 @@
         <v>4.09</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0506</v>
+        <v>0.0608</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0547</v>
+        <v>0.0667</v>
       </c>
       <c r="I87" t="n">
         <v>88</v>
@@ -3604,10 +3604,10 @@
         <v>4.09</v>
       </c>
       <c r="G88" t="n">
-        <v>0.054</v>
+        <v>0.0615</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0584</v>
+        <v>0.0675</v>
       </c>
       <c r="I88" t="n">
         <v>90</v>
@@ -3640,10 +3640,10 @@
         <v>2.79</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0443</v>
+        <v>0.0514</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0702</v>
+        <v>0.0827</v>
       </c>
       <c r="I89" t="n">
         <v>92</v>
@@ -3676,10 +3676,10 @@
         <v>2.79</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0436</v>
+        <v>0.0513</v>
       </c>
       <c r="H90" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0825</v>
       </c>
       <c r="I90" t="n">
         <v>92</v>
@@ -3712,10 +3712,10 @@
         <v>2.79</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0455</v>
+        <v>0.0517</v>
       </c>
       <c r="H91" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="I91" t="n">
         <v>91</v>
@@ -3748,10 +3748,10 @@
         <v>5.04</v>
       </c>
       <c r="G92" t="n">
-        <v>0.1273</v>
+        <v>0.0859</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1118</v>
+        <v>0.0659</v>
       </c>
       <c r="I92" t="n">
         <v>88</v>
@@ -3784,10 +3784,10 @@
         <v>5.04</v>
       </c>
       <c r="G93" t="n">
-        <v>0.1273</v>
+        <v>0.0859</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1118</v>
+        <v>0.0659</v>
       </c>
       <c r="I93" t="n">
         <v>91</v>
@@ -3820,10 +3820,10 @@
         <v>5.04</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1236</v>
+        <v>0.0851</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1085</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="I94" t="n">
         <v>93</v>
@@ -3856,10 +3856,10 @@
         <v>6.49</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0517</v>
+        <v>0.066</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0352</v>
+        <v>0.0456</v>
       </c>
       <c r="I95" t="n">
         <v>89</v>
@@ -3892,10 +3892,10 @@
         <v>6.49</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0536</v>
+        <v>0.0664</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0365</v>
+        <v>0.0459</v>
       </c>
       <c r="I96" t="n">
         <v>89</v>
@@ -3928,10 +3928,10 @@
         <v>6.49</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0531</v>
+        <v>0.0663</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0362</v>
+        <v>0.0458</v>
       </c>
       <c r="I97" t="n">
         <v>91</v>
@@ -3964,10 +3964,10 @@
         <v>4.29</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0576</v>
+        <v>0.0688</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0594</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I98" t="n">
         <v>92</v>
@@ -4000,10 +4000,10 @@
         <v>4.29</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0563</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0581</v>
+        <v>0.0717</v>
       </c>
       <c r="I99" t="n">
         <v>90</v>
@@ -4036,10 +4036,10 @@
         <v>4.29</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0594</v>
+        <v>0.0692</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0612</v>
+        <v>0.0723</v>
       </c>
       <c r="I100" t="n">
         <v>88</v>
@@ -4072,10 +4072,10 @@
         <v>4.09</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0511</v>
+        <v>0.0609</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0553</v>
+        <v>0.0668</v>
       </c>
       <c r="I101" t="n">
         <v>88</v>
@@ -4108,10 +4108,10 @@
         <v>4.09</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0539</v>
+        <v>0.0615</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0583</v>
+        <v>0.0675</v>
       </c>
       <c r="I102" t="n">
         <v>89</v>
@@ -4144,10 +4144,10 @@
         <v>4.09</v>
       </c>
       <c r="G103" t="n">
-        <v>0.051</v>
+        <v>0.0609</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0552</v>
+        <v>0.0668</v>
       </c>
       <c r="I103" t="n">
         <v>88</v>
@@ -4180,10 +4180,10 @@
         <v>2.79</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0437</v>
+        <v>0.0513</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0694</v>
+        <v>0.0825</v>
       </c>
       <c r="I104" t="n">
         <v>91</v>
@@ -4216,10 +4216,10 @@
         <v>2.79</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0463</v>
+        <v>0.0519</v>
       </c>
       <c r="H105" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0834</v>
       </c>
       <c r="I105" t="n">
         <v>88</v>
@@ -4252,10 +4252,10 @@
         <v>2.79</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0439</v>
+        <v>0.0513</v>
       </c>
       <c r="H106" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="I106" t="n">
         <v>90</v>
@@ -4288,10 +4288,10 @@
         <v>5.04</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1259</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1103</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="I107" t="n">
         <v>93</v>
@@ -4324,10 +4324,10 @@
         <v>5.04</v>
       </c>
       <c r="G108" t="n">
-        <v>0.1248</v>
+        <v>0.0853</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1093</v>
+        <v>0.0654</v>
       </c>
       <c r="I108" t="n">
         <v>87</v>
@@ -4360,10 +4360,10 @@
         <v>5.04</v>
       </c>
       <c r="G109" t="n">
-        <v>0.121</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>0.106</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="I109" t="n">
         <v>90</v>
@@ -4396,10 +4396,10 @@
         <v>6.49</v>
       </c>
       <c r="G110" t="n">
-        <v>0.054</v>
+        <v>0.0665</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0367</v>
+        <v>0.046</v>
       </c>
       <c r="I110" t="n">
         <v>91</v>
@@ -4432,10 +4432,10 @@
         <v>6.49</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0536</v>
+        <v>0.0664</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0365</v>
+        <v>0.0459</v>
       </c>
       <c r="I111" t="n">
         <v>88</v>
@@ -4468,10 +4468,10 @@
         <v>6.49</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0537</v>
+        <v>0.0664</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0365</v>
+        <v>0.0459</v>
       </c>
       <c r="I112" t="n">
         <v>88</v>
@@ -4504,10 +4504,10 @@
         <v>4.29</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0568</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0584</v>
+        <v>0.0718</v>
       </c>
       <c r="I113" t="n">
         <v>90</v>
@@ -4540,10 +4540,10 @@
         <v>4.29</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0567</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0584</v>
+        <v>0.0717</v>
       </c>
       <c r="I114" t="n">
         <v>92</v>
@@ -4576,10 +4576,10 @@
         <v>4.29</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0605</v>
+        <v>0.0694</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0623</v>
+        <v>0.0726</v>
       </c>
       <c r="I115" t="n">
         <v>90</v>
@@ -4612,10 +4612,10 @@
         <v>4.09</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0519</v>
+        <v>0.0611</v>
       </c>
       <c r="H116" t="n">
-        <v>0.056</v>
+        <v>0.067</v>
       </c>
       <c r="I116" t="n">
         <v>92</v>
@@ -4648,10 +4648,10 @@
         <v>4.09</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0515</v>
+        <v>0.061</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0556</v>
+        <v>0.0669</v>
       </c>
       <c r="I117" t="n">
         <v>91</v>
@@ -4684,10 +4684,10 @@
         <v>4.09</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0523</v>
+        <v>0.0612</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0564</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="I118" t="n">
         <v>90</v>
@@ -4720,10 +4720,10 @@
         <v>2.79</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0459</v>
+        <v>0.0518</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0726</v>
+        <v>0.0832</v>
       </c>
       <c r="I119" t="n">
         <v>91</v>
@@ -4756,10 +4756,10 @@
         <v>2.79</v>
       </c>
       <c r="G120" t="n">
-        <v>0.047</v>
+        <v>0.052</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0743</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="I120" t="n">
         <v>88</v>
@@ -4792,10 +4792,10 @@
         <v>2.79</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0445</v>
+        <v>0.0515</v>
       </c>
       <c r="H121" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0828</v>
       </c>
       <c r="I121" t="n">
         <v>88</v>
@@ -4828,10 +4828,10 @@
         <v>6.29</v>
       </c>
       <c r="G122" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0465</v>
+        <v>0.0525</v>
       </c>
       <c r="I122" t="n">
         <v>91</v>
@@ -4864,10 +4864,10 @@
         <v>6.29</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0654</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0464</v>
+        <v>0.0525</v>
       </c>
       <c r="I123" t="n">
         <v>92</v>
@@ -4900,10 +4900,10 @@
         <v>6.29</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0626</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0444</v>
+        <v>0.0521</v>
       </c>
       <c r="I124" t="n">
         <v>88</v>
@@ -4936,10 +4936,10 @@
         <v>6.49</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0726</v>
+        <v>0.0702</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0499</v>
+        <v>0.0487</v>
       </c>
       <c r="I125" t="n">
         <v>88</v>
@@ -4972,10 +4972,10 @@
         <v>6.49</v>
       </c>
       <c r="G126" t="n">
-        <v>0.073</v>
+        <v>0.0703</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0502</v>
+        <v>0.0487</v>
       </c>
       <c r="I126" t="n">
         <v>90</v>
@@ -5008,10 +5008,10 @@
         <v>6.49</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0745</v>
+        <v>0.0706</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0512</v>
+        <v>0.0489</v>
       </c>
       <c r="I127" t="n">
         <v>88</v>
@@ -5044,10 +5044,10 @@
         <v>4.29</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0751</v>
+        <v>0.0723</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0781</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="I128" t="n">
         <v>92</v>
@@ -5080,10 +5080,10 @@
         <v>4.29</v>
       </c>
       <c r="G129" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0721</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0769</v>
+        <v>0.0756</v>
       </c>
       <c r="I129" t="n">
         <v>89</v>
@@ -5116,10 +5116,10 @@
         <v>4.29</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0737</v>
+        <v>0.0721</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0766</v>
+        <v>0.0755</v>
       </c>
       <c r="I130" t="n">
         <v>88</v>
@@ -5152,10 +5152,10 @@
         <v>4.09</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0655</v>
+        <v>0.0638</v>
       </c>
       <c r="H131" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0702</v>
       </c>
       <c r="I131" t="n">
         <v>92</v>
@@ -5188,10 +5188,10 @@
         <v>4.09</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0667</v>
+        <v>0.0641</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0728</v>
+        <v>0.0704</v>
       </c>
       <c r="I132" t="n">
         <v>88</v>
@@ -5224,10 +5224,10 @@
         <v>4.09</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0678</v>
+        <v>0.0643</v>
       </c>
       <c r="H133" t="n">
-        <v>0.074</v>
+        <v>0.0706</v>
       </c>
       <c r="I133" t="n">
         <v>89</v>
@@ -5260,10 +5260,10 @@
         <v>2.79</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0551</v>
+        <v>0.0536</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0882</v>
+        <v>0.0864</v>
       </c>
       <c r="I134" t="n">
         <v>88</v>
@@ -5296,10 +5296,10 @@
         <v>2.79</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0542</v>
+        <v>0.0535</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0867</v>
+        <v>0.0861</v>
       </c>
       <c r="I135" t="n">
         <v>88</v>
@@ -5332,10 +5332,10 @@
         <v>2.79</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0542</v>
+        <v>0.0535</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0866</v>
+        <v>0.0861</v>
       </c>
       <c r="I136" t="n">
         <v>88</v>
@@ -5368,10 +5368,10 @@
         <v>6.29</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0643</v>
+        <v>0.0732</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0455</v>
+        <v>0.0523</v>
       </c>
       <c r="I137" t="n">
         <v>90</v>
@@ -5404,10 +5404,10 @@
         <v>6.29</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0649</v>
+        <v>0.0733</v>
       </c>
       <c r="H138" t="n">
-        <v>0.046</v>
+        <v>0.0524</v>
       </c>
       <c r="I138" t="n">
         <v>88</v>
@@ -5440,10 +5440,10 @@
         <v>6.29</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0643</v>
+        <v>0.0732</v>
       </c>
       <c r="H139" t="n">
-        <v>0.0455</v>
+        <v>0.0523</v>
       </c>
       <c r="I139" t="n">
         <v>89</v>
@@ -5476,10 +5476,10 @@
         <v>6.49</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0733</v>
+        <v>0.0704</v>
       </c>
       <c r="H140" t="n">
-        <v>0.0504</v>
+        <v>0.0487</v>
       </c>
       <c r="I140" t="n">
         <v>90</v>
@@ -5512,10 +5512,10 @@
         <v>6.49</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0738</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0507</v>
+        <v>0.0488</v>
       </c>
       <c r="I141" t="n">
         <v>88</v>
@@ -5548,10 +5548,10 @@
         <v>6.49</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0722</v>
+        <v>0.0702</v>
       </c>
       <c r="H142" t="n">
-        <v>0.0496</v>
+        <v>0.0486</v>
       </c>
       <c r="I142" t="n">
         <v>92</v>
@@ -5584,10 +5584,10 @@
         <v>4.29</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0738</v>
+        <v>0.0721</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0766</v>
+        <v>0.0755</v>
       </c>
       <c r="I143" t="n">
         <v>88</v>
@@ -5620,10 +5620,10 @@
         <v>4.29</v>
       </c>
       <c r="G144" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0723</v>
       </c>
       <c r="H144" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0757</v>
       </c>
       <c r="I144" t="n">
         <v>92</v>
@@ -5656,10 +5656,10 @@
         <v>4.29</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0771</v>
+        <v>0.0727</v>
       </c>
       <c r="H145" t="n">
-        <v>0.0801</v>
+        <v>0.0761</v>
       </c>
       <c r="I145" t="n">
         <v>88</v>
@@ -5692,10 +5692,10 @@
         <v>4.09</v>
       </c>
       <c r="G146" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0643</v>
       </c>
       <c r="H146" t="n">
-        <v>0.0742</v>
+        <v>0.0707</v>
       </c>
       <c r="I146" t="n">
         <v>92</v>
@@ -5728,10 +5728,10 @@
         <v>4.09</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0638</v>
+        <v>0.0635</v>
       </c>
       <c r="H147" t="n">
-        <v>0.0696</v>
+        <v>0.0698</v>
       </c>
       <c r="I147" t="n">
         <v>92</v>
@@ -5764,10 +5764,10 @@
         <v>4.09</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0646</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H148" t="n">
-        <v>0.0704</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I148" t="n">
         <v>92</v>
@@ -5800,10 +5800,10 @@
         <v>2.79</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0545</v>
+        <v>0.0535</v>
       </c>
       <c r="H149" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0862</v>
       </c>
       <c r="I149" t="n">
         <v>91</v>
@@ -5836,10 +5836,10 @@
         <v>2.79</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0545</v>
+        <v>0.0535</v>
       </c>
       <c r="H150" t="n">
-        <v>0.0871</v>
+        <v>0.0862</v>
       </c>
       <c r="I150" t="n">
         <v>91</v>
@@ -5872,10 +5872,10 @@
         <v>2.79</v>
       </c>
       <c r="G151" t="n">
-        <v>0.056</v>
+        <v>0.0538</v>
       </c>
       <c r="H151" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0866</v>
       </c>
       <c r="I151" t="n">
         <v>91</v>
@@ -5908,10 +5908,10 @@
         <v>6.29</v>
       </c>
       <c r="G152" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0506</v>
+        <v>0.0532</v>
       </c>
       <c r="I152" t="n">
         <v>89</v>
@@ -5944,10 +5944,10 @@
         <v>6.29</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0674</v>
+        <v>0.0737</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0481</v>
+        <v>0.0527</v>
       </c>
       <c r="I153" t="n">
         <v>89</v>
@@ -5980,10 +5980,10 @@
         <v>6.29</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0697</v>
+        <v>0.0741</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0496</v>
+        <v>0.053</v>
       </c>
       <c r="I154" t="n">
         <v>91</v>
@@ -6016,10 +6016,10 @@
         <v>6.49</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0717</v>
+        <v>0.0701</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0496</v>
+        <v>0.0486</v>
       </c>
       <c r="I155" t="n">
         <v>89</v>
@@ -6052,10 +6052,10 @@
         <v>6.49</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0737</v>
+        <v>0.0704</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0509</v>
+        <v>0.0488</v>
       </c>
       <c r="I156" t="n">
         <v>92</v>
@@ -6088,10 +6088,10 @@
         <v>6.49</v>
       </c>
       <c r="G157" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0494</v>
+        <v>0.0486</v>
       </c>
       <c r="I157" t="n">
         <v>92</v>
@@ -6124,10 +6124,10 @@
         <v>4.29</v>
       </c>
       <c r="G158" t="n">
-        <v>0.073</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H158" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0755</v>
       </c>
       <c r="I158" t="n">
         <v>90</v>
@@ -6160,10 +6160,10 @@
         <v>4.29</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0745</v>
+        <v>0.0722</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0779</v>
+        <v>0.0757</v>
       </c>
       <c r="I159" t="n">
         <v>89</v>
@@ -6196,10 +6196,10 @@
         <v>4.29</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0723</v>
+        <v>0.0718</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0756</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I160" t="n">
         <v>90</v>
@@ -6232,10 +6232,10 @@
         <v>4.09</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0634</v>
+        <v>0.0635</v>
       </c>
       <c r="H161" t="n">
-        <v>0.0694</v>
+        <v>0.0698</v>
       </c>
       <c r="I161" t="n">
         <v>92</v>
@@ -6268,10 +6268,10 @@
         <v>4.09</v>
       </c>
       <c r="G162" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0638</v>
       </c>
       <c r="H162" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="I162" t="n">
         <v>91</v>
@@ -6304,10 +6304,10 @@
         <v>4.09</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0648</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H163" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0701</v>
       </c>
       <c r="I163" t="n">
         <v>91</v>
@@ -6340,10 +6340,10 @@
         <v>2.79</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0536</v>
+        <v>0.0534</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0861</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I164" t="n">
         <v>90</v>
@@ -6376,10 +6376,10 @@
         <v>2.79</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0542</v>
+        <v>0.0535</v>
       </c>
       <c r="H165" t="n">
-        <v>0.0871</v>
+        <v>0.0862</v>
       </c>
       <c r="I165" t="n">
         <v>91</v>
@@ -6412,10 +6412,10 @@
         <v>2.79</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0542</v>
+        <v>0.0535</v>
       </c>
       <c r="H166" t="n">
-        <v>0.0871</v>
+        <v>0.0862</v>
       </c>
       <c r="I166" t="n">
         <v>89</v>
@@ -6448,10 +6448,10 @@
         <v>6.29</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0733</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0522</v>
+        <v>0.0535</v>
       </c>
       <c r="I167" t="n">
         <v>91</v>
@@ -6484,10 +6484,10 @@
         <v>6.29</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0702</v>
+        <v>0.0742</v>
       </c>
       <c r="H168" t="n">
-        <v>0.05</v>
+        <v>0.0531</v>
       </c>
       <c r="I168" t="n">
         <v>92</v>
@@ -6520,10 +6520,10 @@
         <v>6.29</v>
       </c>
       <c r="G169" t="n">
-        <v>0.073</v>
+        <v>0.0747</v>
       </c>
       <c r="H169" t="n">
-        <v>0.052</v>
+        <v>0.0534</v>
       </c>
       <c r="I169" t="n">
         <v>89</v>
@@ -6556,10 +6556,10 @@
         <v>6.49</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0723</v>
+        <v>0.0702</v>
       </c>
       <c r="H170" t="n">
-        <v>0.0499</v>
+        <v>0.0487</v>
       </c>
       <c r="I170" t="n">
         <v>90</v>
@@ -6592,10 +6592,10 @@
         <v>6.49</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0682</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H171" t="n">
-        <v>0.0471</v>
+        <v>0.0482</v>
       </c>
       <c r="I171" t="n">
         <v>88</v>
@@ -6628,10 +6628,10 @@
         <v>6.49</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0709</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H172" t="n">
-        <v>0.049</v>
+        <v>0.0485</v>
       </c>
       <c r="I172" t="n">
         <v>91</v>
@@ -6664,10 +6664,10 @@
         <v>4.29</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0699</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H173" t="n">
-        <v>0.0731</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I173" t="n">
         <v>88</v>
@@ -6700,10 +6700,10 @@
         <v>4.29</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0736</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H174" t="n">
-        <v>0.0769</v>
+        <v>0.0756</v>
       </c>
       <c r="I174" t="n">
         <v>90</v>
@@ -6736,10 +6736,10 @@
         <v>4.29</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0699</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H175" t="n">
-        <v>0.073</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I175" t="n">
         <v>90</v>
@@ -6772,10 +6772,10 @@
         <v>4.09</v>
       </c>
       <c r="G176" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="H176" t="n">
-        <v>0.0726</v>
+        <v>0.0704</v>
       </c>
       <c r="I176" t="n">
         <v>90</v>
@@ -6808,10 +6808,10 @@
         <v>4.09</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0621</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="H177" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0696</v>
       </c>
       <c r="I177" t="n">
         <v>90</v>
@@ -6844,10 +6844,10 @@
         <v>4.09</v>
       </c>
       <c r="G178" t="n">
-        <v>0.0663</v>
+        <v>0.064</v>
       </c>
       <c r="H178" t="n">
-        <v>0.0727</v>
+        <v>0.0704</v>
       </c>
       <c r="I178" t="n">
         <v>91</v>
@@ -6880,10 +6880,10 @@
         <v>2.79</v>
       </c>
       <c r="G179" t="n">
-        <v>0.055</v>
+        <v>0.0536</v>
       </c>
       <c r="H179" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0864</v>
       </c>
       <c r="I179" t="n">
         <v>91</v>
@@ -6916,10 +6916,10 @@
         <v>2.79</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0541</v>
+        <v>0.0534</v>
       </c>
       <c r="H180" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0862</v>
       </c>
       <c r="I180" t="n">
         <v>90</v>
@@ -6952,10 +6952,10 @@
         <v>2.79</v>
       </c>
       <c r="G181" t="n">
-        <v>0.0549</v>
+        <v>0.0536</v>
       </c>
       <c r="H181" t="n">
-        <v>0.0882</v>
+        <v>0.0864</v>
       </c>
       <c r="I181" t="n">
         <v>90</v>
@@ -6988,10 +6988,10 @@
         <v>6.29</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0786</v>
+        <v>0.0795</v>
       </c>
       <c r="H182" t="n">
-        <v>0.0561</v>
+        <v>0.0571</v>
       </c>
       <c r="I182" t="n">
         <v>88</v>
@@ -7024,10 +7024,10 @@
         <v>6.29</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0736</v>
+        <v>0.0786</v>
       </c>
       <c r="H183" t="n">
-        <v>0.0526</v>
+        <v>0.0565</v>
       </c>
       <c r="I183" t="n">
         <v>92</v>
@@ -7060,10 +7060,10 @@
         <v>6.29</v>
       </c>
       <c r="G184" t="n">
-        <v>0.0736</v>
+        <v>0.0786</v>
       </c>
       <c r="H184" t="n">
-        <v>0.0526</v>
+        <v>0.0565</v>
       </c>
       <c r="I184" t="n">
         <v>90</v>
@@ -7096,10 +7096,10 @@
         <v>6.49</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0655</v>
+        <v>0.068</v>
       </c>
       <c r="H185" t="n">
-        <v>0.0453</v>
+        <v>0.0473</v>
       </c>
       <c r="I185" t="n">
         <v>89</v>
@@ -7132,10 +7132,10 @@
         <v>6.49</v>
       </c>
       <c r="G186" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="H186" t="n">
-        <v>0.0475</v>
+        <v>0.0477</v>
       </c>
       <c r="I186" t="n">
         <v>91</v>
@@ -7168,10 +7168,10 @@
         <v>6.49</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0673</v>
+        <v>0.0683</v>
       </c>
       <c r="H187" t="n">
-        <v>0.0466</v>
+        <v>0.0476</v>
       </c>
       <c r="I187" t="n">
         <v>90</v>
@@ -7204,10 +7204,10 @@
         <v>4.29</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0741</v>
+        <v>0.0711</v>
       </c>
       <c r="H188" t="n">
-        <v>0.0776</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I188" t="n">
         <v>92</v>
@@ -7240,10 +7240,10 @@
         <v>4.29</v>
       </c>
       <c r="G189" t="n">
-        <v>0.0735</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H189" t="n">
-        <v>0.077</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I189" t="n">
         <v>91</v>
@@ -7276,10 +7276,10 @@
         <v>4.29</v>
       </c>
       <c r="G190" t="n">
-        <v>0.0716</v>
+        <v>0.0706</v>
       </c>
       <c r="H190" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="I190" t="n">
         <v>90</v>
@@ -7312,10 +7312,10 @@
         <v>4.09</v>
       </c>
       <c r="G191" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="H191" t="n">
-        <v>0.0728</v>
+        <v>0.0697</v>
       </c>
       <c r="I191" t="n">
         <v>89</v>
@@ -7348,10 +7348,10 @@
         <v>4.09</v>
       </c>
       <c r="G192" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0629</v>
       </c>
       <c r="H192" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="I192" t="n">
         <v>92</v>
@@ -7384,10 +7384,10 @@
         <v>4.09</v>
       </c>
       <c r="G193" t="n">
-        <v>0.063</v>
+        <v>0.0625</v>
       </c>
       <c r="H193" t="n">
-        <v>0.0692</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I193" t="n">
         <v>91</v>
@@ -7420,10 +7420,10 @@
         <v>2.79</v>
       </c>
       <c r="G194" t="n">
-        <v>0.0533</v>
+        <v>0.0525</v>
       </c>
       <c r="H194" t="n">
-        <v>0.0859</v>
+        <v>0.0851</v>
       </c>
       <c r="I194" t="n">
         <v>92</v>
@@ -7456,10 +7456,10 @@
         <v>2.79</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0531</v>
+        <v>0.0525</v>
       </c>
       <c r="H195" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I195" t="n">
         <v>88</v>
@@ -7495,7 +7495,7 @@
         <v>0.0524</v>
       </c>
       <c r="H196" t="n">
-        <v>0.0844</v>
+        <v>0.0848</v>
       </c>
       <c r="I196" t="n">
         <v>92</v>
@@ -7528,10 +7528,10 @@
         <v>6.29</v>
       </c>
       <c r="G197" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0793</v>
       </c>
       <c r="H197" t="n">
-        <v>0.0555</v>
+        <v>0.057</v>
       </c>
       <c r="I197" t="n">
         <v>92</v>
@@ -7564,10 +7564,10 @@
         <v>6.29</v>
       </c>
       <c r="G198" t="n">
-        <v>0.0746</v>
+        <v>0.0788</v>
       </c>
       <c r="H198" t="n">
-        <v>0.0532</v>
+        <v>0.0566</v>
       </c>
       <c r="I198" t="n">
         <v>89</v>
@@ -7600,10 +7600,10 @@
         <v>6.29</v>
       </c>
       <c r="G199" t="n">
-        <v>0.0774</v>
+        <v>0.0793</v>
       </c>
       <c r="H199" t="n">
-        <v>0.0553</v>
+        <v>0.057</v>
       </c>
       <c r="I199" t="n">
         <v>92</v>
@@ -7636,10 +7636,10 @@
         <v>6.49</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0682</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="H200" t="n">
-        <v>0.0472</v>
+        <v>0.0477</v>
       </c>
       <c r="I200" t="n">
         <v>88</v>
@@ -7672,10 +7672,10 @@
         <v>6.49</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0646</v>
+        <v>0.0678</v>
       </c>
       <c r="H201" t="n">
-        <v>0.0447</v>
+        <v>0.0472</v>
       </c>
       <c r="I201" t="n">
         <v>92</v>
@@ -7708,10 +7708,10 @@
         <v>6.49</v>
       </c>
       <c r="G202" t="n">
-        <v>0.067</v>
+        <v>0.0682</v>
       </c>
       <c r="H202" t="n">
-        <v>0.0463</v>
+        <v>0.0475</v>
       </c>
       <c r="I202" t="n">
         <v>91</v>
@@ -7744,10 +7744,10 @@
         <v>4.29</v>
       </c>
       <c r="G203" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H203" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I203" t="n">
         <v>91</v>
@@ -7780,10 +7780,10 @@
         <v>4.29</v>
       </c>
       <c r="G204" t="n">
-        <v>0.0708</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="H204" t="n">
-        <v>0.0741</v>
+        <v>0.0743</v>
       </c>
       <c r="I204" t="n">
         <v>88</v>
@@ -7816,10 +7816,10 @@
         <v>4.29</v>
       </c>
       <c r="G205" t="n">
-        <v>0.0717</v>
+        <v>0.0707</v>
       </c>
       <c r="H205" t="n">
-        <v>0.0751</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="I205" t="n">
         <v>92</v>
@@ -7852,10 +7852,10 @@
         <v>4.09</v>
       </c>
       <c r="G206" t="n">
-        <v>0.0634</v>
+        <v>0.0626</v>
       </c>
       <c r="H206" t="n">
-        <v>0.0696</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="I206" t="n">
         <v>88</v>
@@ -7888,10 +7888,10 @@
         <v>4.09</v>
       </c>
       <c r="G207" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0624</v>
       </c>
       <c r="H207" t="n">
-        <v>0.0688</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I207" t="n">
         <v>89</v>
@@ -7924,10 +7924,10 @@
         <v>4.09</v>
       </c>
       <c r="G208" t="n">
-        <v>0.0659</v>
+        <v>0.063</v>
       </c>
       <c r="H208" t="n">
-        <v>0.0723</v>
+        <v>0.0696</v>
       </c>
       <c r="I208" t="n">
         <v>88</v>
@@ -7960,10 +7960,10 @@
         <v>2.79</v>
       </c>
       <c r="G209" t="n">
-        <v>0.0547</v>
+        <v>0.0528</v>
       </c>
       <c r="H209" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="I209" t="n">
         <v>91</v>
@@ -7996,10 +7996,10 @@
         <v>2.79</v>
       </c>
       <c r="G210" t="n">
-        <v>0.0518</v>
+        <v>0.0523</v>
       </c>
       <c r="H210" t="n">
-        <v>0.0834</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="I210" t="n">
         <v>89</v>
@@ -8032,10 +8032,10 @@
         <v>2.79</v>
       </c>
       <c r="G211" t="n">
-        <v>0.0556</v>
+        <v>0.0529</v>
       </c>
       <c r="H211" t="n">
-        <v>0.0895</v>
+        <v>0.0857</v>
       </c>
       <c r="I211" t="n">
         <v>92</v>
@@ -8068,10 +8068,10 @@
         <v>6.29</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0786</v>
+        <v>0.0795</v>
       </c>
       <c r="H212" t="n">
-        <v>0.0561</v>
+        <v>0.0571</v>
       </c>
       <c r="I212" t="n">
         <v>89</v>
@@ -8104,10 +8104,10 @@
         <v>6.29</v>
       </c>
       <c r="G213" t="n">
-        <v>0.0747</v>
+        <v>0.0788</v>
       </c>
       <c r="H213" t="n">
-        <v>0.0534</v>
+        <v>0.0566</v>
       </c>
       <c r="I213" t="n">
         <v>88</v>
@@ -8140,10 +8140,10 @@
         <v>6.29</v>
       </c>
       <c r="G214" t="n">
-        <v>0.0745</v>
+        <v>0.0788</v>
       </c>
       <c r="H214" t="n">
-        <v>0.0532</v>
+        <v>0.0566</v>
       </c>
       <c r="I214" t="n">
         <v>90</v>
@@ -8176,10 +8176,10 @@
         <v>6.49</v>
       </c>
       <c r="G215" t="n">
-        <v>0.0648</v>
+        <v>0.0678</v>
       </c>
       <c r="H215" t="n">
-        <v>0.0448</v>
+        <v>0.0472</v>
       </c>
       <c r="I215" t="n">
         <v>91</v>
@@ -8212,10 +8212,10 @@
         <v>6.49</v>
       </c>
       <c r="G216" t="n">
-        <v>0.0677</v>
+        <v>0.0684</v>
       </c>
       <c r="H216" t="n">
-        <v>0.0469</v>
+        <v>0.0476</v>
       </c>
       <c r="I216" t="n">
         <v>91</v>
@@ -8248,10 +8248,10 @@
         <v>6.49</v>
       </c>
       <c r="G217" t="n">
-        <v>0.0688</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="H217" t="n">
-        <v>0.0476</v>
+        <v>0.0477</v>
       </c>
       <c r="I217" t="n">
         <v>92</v>
@@ -8284,10 +8284,10 @@
         <v>4.29</v>
       </c>
       <c r="G218" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0704</v>
       </c>
       <c r="H218" t="n">
-        <v>0.0737</v>
+        <v>0.0742</v>
       </c>
       <c r="I218" t="n">
         <v>88</v>
@@ -8320,10 +8320,10 @@
         <v>4.29</v>
       </c>
       <c r="G219" t="n">
-        <v>0.074</v>
+        <v>0.0711</v>
       </c>
       <c r="H219" t="n">
-        <v>0.0774</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I219" t="n">
         <v>91</v>
@@ -8356,10 +8356,10 @@
         <v>4.29</v>
       </c>
       <c r="G220" t="n">
-        <v>0.0694</v>
+        <v>0.0703</v>
       </c>
       <c r="H220" t="n">
-        <v>0.0727</v>
+        <v>0.074</v>
       </c>
       <c r="I220" t="n">
         <v>89</v>
@@ -8392,10 +8392,10 @@
         <v>4.09</v>
       </c>
       <c r="G221" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0629</v>
       </c>
       <c r="H221" t="n">
-        <v>0.0716</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="I221" t="n">
         <v>89</v>
@@ -8428,10 +8428,10 @@
         <v>4.09</v>
       </c>
       <c r="G222" t="n">
-        <v>0.0659</v>
+        <v>0.063</v>
       </c>
       <c r="H222" t="n">
-        <v>0.0723</v>
+        <v>0.0696</v>
       </c>
       <c r="I222" t="n">
         <v>91</v>
@@ -8464,10 +8464,10 @@
         <v>4.09</v>
       </c>
       <c r="G223" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="H223" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0694</v>
       </c>
       <c r="I223" t="n">
         <v>92</v>
@@ -8500,10 +8500,10 @@
         <v>2.79</v>
       </c>
       <c r="G224" t="n">
-        <v>0.0543</v>
+        <v>0.0527</v>
       </c>
       <c r="H224" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0854</v>
       </c>
       <c r="I224" t="n">
         <v>91</v>
@@ -8536,10 +8536,10 @@
         <v>2.79</v>
       </c>
       <c r="G225" t="n">
-        <v>0.0549</v>
+        <v>0.0528</v>
       </c>
       <c r="H225" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0856</v>
       </c>
       <c r="I225" t="n">
         <v>88</v>
@@ -8572,10 +8572,10 @@
         <v>2.79</v>
       </c>
       <c r="G226" t="n">
-        <v>0.0515</v>
+        <v>0.0522</v>
       </c>
       <c r="H226" t="n">
-        <v>0.0829</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="I226" t="n">
         <v>91</v>
@@ -8608,10 +8608,10 @@
         <v>6.29</v>
       </c>
       <c r="G227" t="n">
-        <v>0.0746</v>
+        <v>0.0788</v>
       </c>
       <c r="H227" t="n">
-        <v>0.0533</v>
+        <v>0.0566</v>
       </c>
       <c r="I227" t="n">
         <v>91</v>
@@ -8644,10 +8644,10 @@
         <v>6.29</v>
       </c>
       <c r="G228" t="n">
-        <v>0.0799</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="H228" t="n">
-        <v>0.057</v>
+        <v>0.0573</v>
       </c>
       <c r="I228" t="n">
         <v>91</v>
@@ -8680,10 +8680,10 @@
         <v>6.29</v>
       </c>
       <c r="G229" t="n">
-        <v>0.0788</v>
+        <v>0.0795</v>
       </c>
       <c r="H229" t="n">
-        <v>0.0562</v>
+        <v>0.0571</v>
       </c>
       <c r="I229" t="n">
         <v>92</v>
@@ -8716,10 +8716,10 @@
         <v>6.49</v>
       </c>
       <c r="G230" t="n">
-        <v>0.0653</v>
+        <v>0.0679</v>
       </c>
       <c r="H230" t="n">
-        <v>0.0452</v>
+        <v>0.0473</v>
       </c>
       <c r="I230" t="n">
         <v>88</v>
@@ -8752,10 +8752,10 @@
         <v>6.49</v>
       </c>
       <c r="G231" t="n">
-        <v>0.0649</v>
+        <v>0.0679</v>
       </c>
       <c r="H231" t="n">
-        <v>0.0449</v>
+        <v>0.0472</v>
       </c>
       <c r="I231" t="n">
         <v>90</v>
@@ -8788,10 +8788,10 @@
         <v>6.49</v>
       </c>
       <c r="G232" t="n">
-        <v>0.0654</v>
+        <v>0.0679</v>
       </c>
       <c r="H232" t="n">
-        <v>0.0452</v>
+        <v>0.0473</v>
       </c>
       <c r="I232" t="n">
         <v>90</v>
@@ -8824,10 +8824,10 @@
         <v>4.29</v>
       </c>
       <c r="G233" t="n">
-        <v>0.0746</v>
+        <v>0.0712</v>
       </c>
       <c r="H233" t="n">
-        <v>0.078</v>
+        <v>0.075</v>
       </c>
       <c r="I233" t="n">
         <v>90</v>
@@ -8860,10 +8860,10 @@
         <v>4.29</v>
       </c>
       <c r="G234" t="n">
-        <v>0.0716</v>
+        <v>0.0706</v>
       </c>
       <c r="H234" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="I234" t="n">
         <v>88</v>
@@ -8896,10 +8896,10 @@
         <v>4.29</v>
       </c>
       <c r="G235" t="n">
-        <v>0.0735</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H235" t="n">
-        <v>0.0769</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I235" t="n">
         <v>88</v>
@@ -8932,10 +8932,10 @@
         <v>4.09</v>
       </c>
       <c r="G236" t="n">
-        <v>0.0643</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="H236" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0693</v>
       </c>
       <c r="I236" t="n">
         <v>89</v>
@@ -8968,10 +8968,10 @@
         <v>4.09</v>
       </c>
       <c r="G237" t="n">
-        <v>0.064</v>
+        <v>0.0626</v>
       </c>
       <c r="H237" t="n">
-        <v>0.0702</v>
+        <v>0.0692</v>
       </c>
       <c r="I237" t="n">
         <v>89</v>
@@ -9004,10 +9004,10 @@
         <v>4.09</v>
       </c>
       <c r="G238" t="n">
-        <v>0.0618</v>
+        <v>0.0623</v>
       </c>
       <c r="H238" t="n">
-        <v>0.0678</v>
+        <v>0.0688</v>
       </c>
       <c r="I238" t="n">
         <v>90</v>
@@ -9040,10 +9040,10 @@
         <v>2.79</v>
       </c>
       <c r="G239" t="n">
-        <v>0.0553</v>
+        <v>0.0529</v>
       </c>
       <c r="H239" t="n">
-        <v>0.089</v>
+        <v>0.0857</v>
       </c>
       <c r="I239" t="n">
         <v>91</v>
@@ -9076,10 +9076,10 @@
         <v>2.79</v>
       </c>
       <c r="G240" t="n">
-        <v>0.0525</v>
+        <v>0.0524</v>
       </c>
       <c r="H240" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0849</v>
       </c>
       <c r="I240" t="n">
         <v>91</v>
@@ -9112,10 +9112,10 @@
         <v>2.79</v>
       </c>
       <c r="G241" t="n">
-        <v>0.0537</v>
+        <v>0.0526</v>
       </c>
       <c r="H241" t="n">
-        <v>0.0864</v>
+        <v>0.0852</v>
       </c>
       <c r="I241" t="n">
         <v>90</v>
